--- a/tame_output/ON/bt/strategyON_20241007.xlsx
+++ b/tame_output/ON/bt/strategyON_20241007.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>424.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.6%</t>
+          <t>-668.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.2%</t>
+          <t>-118.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.1%</t>
+          <t>-203.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-97.7%</t>
+          <t>-98.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.3%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.160862811117614</v>
+        <v>-4.166429528281172</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6954849025329342</v>
+        <v>0.6932582156675111</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.116489679479045</v>
+        <v>-4.122056396642603</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7130970226237978</v>
+        <v>0.7108703357583748</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.081758358160545</v>
+        <v>-4.087325075324102</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7213833452897886</v>
+        <v>0.7191566584243654</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.034102627599489</v>
+        <v>-4.039669344763047</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7468273945420156</v>
+        <v>0.7446007076765924</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.933584469100734</v>
+        <v>-3.939151186264292</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7919270313162423</v>
+        <v>0.789700344450819</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.917679139668381</v>
+        <v>-3.923245856831939</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7850438355650555</v>
+        <v>0.7828171486996323</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.872840738059983</v>
+        <v>-3.878407455223541</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8070768988190433</v>
+        <v>0.8048502119536201</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.892339194301992</v>
+        <v>-3.897905911465549</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8034384559533181</v>
+        <v>0.8012117690878948</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.848136357216091</v>
+        <v>-3.853703074379649</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8269991933155154</v>
+        <v>0.8247725064500921</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.855696023053138</v>
+        <v>-3.861262740216696</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8223853274499442</v>
+        <v>0.8201586405845209</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.697404605513866</v>
+        <v>-3.702971322677424</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9369496596486926</v>
+        <v>0.9347229727832695</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.48976260187939</v>
+        <v>-3.495329319042948</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.018447165696736</v>
+        <v>1.016220478831313</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.438730509156862</v>
+        <v>-3.444297226320419</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.033808231024018</v>
+        <v>1.031581544158594</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.373506328029656</v>
+        <v>-3.379073045193214</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.077085307567605</v>
+        <v>1.074858620702182</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.336079307958522</v>
+        <v>-3.34164602512208</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.088017087895339</v>
+        <v>1.085790401029916</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.334721322984977</v>
+        <v>-3.340288040148534</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.089817074215997</v>
+        <v>1.087590387350574</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.306308059885093</v>
+        <v>-3.311874777048651</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.261740150477161</v>
+        <v>1.259513463611738</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47367,10 +47367,10 @@
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.23152579886008</v>
+        <v>-3.237092516023638</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.411765964104984</v>
+        <v>1.409539277239561</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.205441714596272</v>
+        <v>-3.21100843175983</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.413907573824366</v>
+        <v>1.411680886958943</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47413,10 +47413,10 @@
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.117563801487152</v>
+        <v>-3.12313051865071</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.447251934651793</v>
+        <v>1.44502524778637</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.108671340093869</v>
+        <v>-3.114238057257427</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.468363324935898</v>
+        <v>1.466136638070475</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47459,10 +47459,10 @@
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.277147457063747</v>
+        <v>-3.282714174227304</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.392827925552531</v>
+        <v>1.390601238687108</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47482,10 +47482,10 @@
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.830891264434307</v>
+        <v>-2.836457981597865</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.552600099792169</v>
+        <v>1.550373412926745</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.808170160751154</v>
+        <v>-2.813736877914712</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.552352563762334</v>
+        <v>1.550125876896911</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.937371974045197</v>
+        <v>-2.942938691208755</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.659577964295886</v>
+        <v>1.657351277430463</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47551,10 +47551,10 @@
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.963246372519222</v>
+        <v>-2.96881308968278</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.686306027399923</v>
+        <v>1.684079340534499</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.956191682304049</v>
+        <v>-2.961758399467607</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.685803259475537</v>
+        <v>1.683576572610114</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.929240457977561</v>
+        <v>-2.934807175141119</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.706589902850874</v>
+        <v>1.704363215985451</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.950784685808348</v>
+        <v>-2.956351402971906</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.882075343863519</v>
+        <v>1.879848656998096</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.97319280361322</v>
+        <v>-2.978759520776778</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.865228791644563</v>
+        <v>1.86300210477914</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.00141703919082</v>
+        <v>-3.006983756354378</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.85599309696316</v>
+        <v>1.853766410097737</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.01085796507935</v>
+        <v>-3.016424682242908</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.908470444329595</v>
+        <v>1.906243757464172</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.217096902867784</v>
+        <v>-3.222663620031342</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.828865963759523</v>
+        <v>1.8266392768941</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9241185524652205</v>
@@ -47735,10 +47735,10 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.29342688046869</v>
+        <v>-3.298993597632248</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.796445785612936</v>
+        <v>1.794219098747513</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9241185524652205</v>
@@ -47758,10 +47758,10 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.448383665868819</v>
+        <v>-3.453950383032377</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.729283301055746</v>
+        <v>1.727056614190323</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7691617670650912</v>
@@ -47781,10 +47781,10 @@
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.609952091396074</v>
+        <v>-3.615518808559632</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.663089941054997</v>
+        <v>1.660863254189574</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6423788432672118</v>
@@ -47804,10 +47804,10 @@
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.718252753266194</v>
+        <v>-3.723819470429751</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.632843083172868</v>
+        <v>1.630616396307444</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6423788432672118</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.877803826029711</v>
+        <v>-3.883370543193268</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.561027850850401</v>
+        <v>1.558801163984977</v>
       </c>
       <c r="F2012" t="n">
         <v>0.4901011764054604</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.905704613139183</v>
+        <v>-3.911271330302741</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.548391577133613</v>
+        <v>1.54616489026819</v>
       </c>
       <c r="F2013" t="n">
         <v>0.4555042522625256</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.028230715842078</v>
+        <v>-4.033797433005635</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.496145580029655</v>
+        <v>1.493918893164232</v>
       </c>
       <c r="F2014" t="n">
         <v>0.3329781495596317</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.258745212027667</v>
+        <v>-4.264311929191224</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.470645741145923</v>
+        <v>1.4684190542805</v>
       </c>
       <c r="F2015" t="n">
         <v>0.102463653374043</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781467</v>
+        <v>3.640750087814669</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.60749029725211</v>
+        <v>-4.613057014415667</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.471459426057992</v>
+        <v>1.469232739192569</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.006284300544854848</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237099</v>
+        <v>3.668289004237098</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.761476715028251</v>
+        <v>-4.767043432191808</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.478845128093176</v>
+        <v>1.476618441227753</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.006284300544854848</v>
@@ -47965,10 +47965,10 @@
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.96607614989126</v>
+        <v>-4.971642867054817</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.383056556268093</v>
+        <v>1.380829869402671</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.006284300544854848</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609757</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.218551303898984</v>
+        <v>-5.224118021062541</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.293936983720418</v>
+        <v>1.291710296854995</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.006284300544854848</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.67402853597316</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.511447060378396</v>
+        <v>-5.517013777541953</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.177989215647596</v>
+        <v>1.175762528782174</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.006284300544854848</v>
@@ -48034,10 +48034,10 @@
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.698111188513204</v>
+        <v>-5.703677905676761</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.107445306620995</v>
+        <v>1.105218619755572</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.03302327136941474</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916205</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.844131875427166</v>
+        <v>-5.849698592590723</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.044114884591599</v>
+        <v>1.041888197726176</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.04210636316327171</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.935845884536752</v>
+        <v>-5.941412601700309</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.169633337646809</v>
+        <v>1.167406650781386</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.04210636316327171</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071556</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.967497543596721</v>
+        <v>-5.973064260760278</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.151819311986635</v>
+        <v>1.149592625121213</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.04727482040771191</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868154</v>
+        <v>3.750044015868153</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.036563598169658</v>
+        <v>-6.042130315333215</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.134422307725952</v>
+        <v>1.132195620860529</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1096456979013219</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332701</v>
+        <v>3.783632867332699</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.138539720418065</v>
+        <v>-6.144106437581622</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.102557497282491</v>
+        <v>1.100330810417069</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.2116218201497295</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231818</v>
+        <v>3.798296784231816</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.028533436940844</v>
+        <v>-6.034100154104401</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.138712897917555</v>
+        <v>1.136486211052132</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.1884172482324543</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818525</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.041063142052723</v>
+        <v>-6.04662985921628</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.137951026594778</v>
+        <v>1.135724339729355</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2022437476989773</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051791</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.739616416580885</v>
+        <v>-5.745183133744442</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.265790599666049</v>
+        <v>1.263563912800626</v>
       </c>
       <c r="F2029" t="n">
         <v>0.09920297777285991</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679629</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.764206660816069</v>
+        <v>-5.769773377979626</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.256925679724686</v>
+        <v>1.254698992859264</v>
       </c>
       <c r="F2030" t="n">
         <v>0.09920297777285991</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.713168284809549</v>
+        <v>-5.718735001973106</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.27818393450705</v>
+        <v>1.275957247641627</v>
       </c>
       <c r="F2031" t="n">
         <v>0.09920297777285991</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969548</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.684319607986088</v>
+        <v>-5.689886325149645</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.30876150411058</v>
+        <v>1.306534817245157</v>
       </c>
       <c r="F2032" t="n">
         <v>0.1280516545963202</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700484</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.587684695967448</v>
+        <v>-5.593251413131005</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.16359946504197</v>
+        <v>1.161372778176547</v>
       </c>
       <c r="F2033" t="n">
         <v>0.2246865666149601</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077647</v>
+        <v>3.804688961077644</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.518646685018981</v>
+        <v>-5.524213402182538</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.194716713495321</v>
+        <v>1.192490026629899</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2937245775634282</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833467</v>
+        <v>3.775028860833464</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.499859584650042</v>
+        <v>-5.505426301813599</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.186658372718979</v>
+        <v>1.184431685853557</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3125116779323667</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077632</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.422760983108169</v>
+        <v>-5.428327700271726</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.216685523772158</v>
+        <v>1.214458836906735</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3125116779323667</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147914</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.433146177998059</v>
+        <v>-5.438712895161616</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.222400224941275</v>
+        <v>1.220173538075852</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3021264830424774</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373529</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.451734336720284</v>
+        <v>-5.457301053883841</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.28580196722881</v>
+        <v>1.283575280363387</v>
       </c>
       <c r="F2038" t="n">
         <v>0.283538324320252</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496559</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.45203288341632</v>
+        <v>-5.457599600579877</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.282551559368694</v>
+        <v>1.280324872503271</v>
       </c>
       <c r="F2039" t="n">
         <v>0.2832397776242161</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108865</v>
+        <v>3.815643212108862</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.351209749725892</v>
+        <v>-5.356776466889449</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.327411707784257</v>
+        <v>1.325185020918834</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2957039931085699</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121477</v>
+        <v>3.807356168121474</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.160428388973484</v>
+        <v>-5.165995106137041</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.403853505563763</v>
+        <v>1.40162681869834</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4864853538609773</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390609</v>
+        <v>3.775233033906087</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.053465031124063</v>
+        <v>-5.059031748287619</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.426475694441128</v>
+        <v>1.424249007575705</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5449499618207787</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912995</v>
+        <v>3.785761685912991</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.9981344432223</v>
+        <v>-5.003701160385857</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.483574866213891</v>
+        <v>1.481348179348469</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6002805497225409</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539904</v>
+        <v>3.743767956539901</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.986080316309337</v>
+        <v>-4.991647033472894</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.482083084880514</v>
+        <v>1.479856398015092</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6123346766355037</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481102</v>
+        <v>3.725010844811016</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.063435806437306</v>
+        <v>-5.069002523600863</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.453021519013463</v>
+        <v>1.45079483214804</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5349791865075343</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438293</v>
+        <v>3.612322444382927</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.995387243745776</v>
+        <v>-5.000953960909333</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.493091969967957</v>
+        <v>1.490865283102534</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6030277491990641</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013437</v>
+        <v>3.645256780013434</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.226987636915277</v>
+        <v>-5.232554354078834</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.420654482873751</v>
+        <v>1.418427796008328</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6030277491990641</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498973</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.277039182444497</v>
+        <v>-5.282605899608054</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.384240100728945</v>
+        <v>1.382013413863522</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800102</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.452146015020942</v>
+        <v>-5.457712732184499</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.274449281291834</v>
+        <v>1.272222594426411</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660855</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.256045861590419</v>
+        <v>-5.261612578753976</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.359911961660983</v>
+        <v>1.35768527479556</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395092</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.103020469477134</v>
+        <v>-5.108587186640691</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.520293118079201</v>
+        <v>1.518066431213778</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791154</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.131327783350405</v>
+        <v>-5.136894500513962</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.696436417438186</v>
+        <v>1.694209730572763</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69911561562044</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.297921008463927</v>
+        <v>-5.303487725627484</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.599202078746859</v>
+        <v>1.596975391881437</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285653</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.274885215102361</v>
+        <v>-5.280451932265918</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.612092798753204</v>
+        <v>1.609866111887781</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399474</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.245639234646664</v>
+        <v>-5.251205951810221</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.621409246058978</v>
+        <v>1.619182559193554</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256377</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.352564782524516</v>
+        <v>-5.358131499688072</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.575932266065472</v>
+        <v>1.573705579200049</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701007</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.497583341031764</v>
+        <v>-5.503150058195321</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.519353644805807</v>
+        <v>1.517126957940384</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687019</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.615925106816482</v>
+        <v>-5.621491823980039</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.571948177749673</v>
+        <v>1.56972149088425</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790811</v>
+        <v>3.714879051790808</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.66733552913719</v>
+        <v>-5.672902246300747</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.549169705947329</v>
+        <v>1.546943019081906</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943734</v>
+        <v>3.704757949437337</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.746754980344941</v>
+        <v>-5.752321697508498</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.517305053538517</v>
+        <v>1.515078366673094</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298408</v>
+        <v>3.736804952298405</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.842217978262159</v>
+        <v>-5.847784695425716</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.479113747929673</v>
+        <v>1.47688706106425</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218011</v>
+        <v>3.715372960218008</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.777842067411444</v>
+        <v>-5.783408784575001</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.50296050883257</v>
+        <v>1.500733821967147</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353547</v>
+        <v>3.736089413353543</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.833211229543638</v>
+        <v>-5.838777946707195</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.486546661727419</v>
+        <v>1.484319974861996</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011329</v>
+        <v>3.736822870113286</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.851429696541246</v>
+        <v>-5.856996413704803</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.478797638271308</v>
+        <v>1.476570951405885</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113699</v>
+        <v>3.790272500113695</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.812746261197316</v>
+        <v>-5.818312978360873</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.514145405259199</v>
+        <v>1.511918718393776</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.706711265992007</v>
+        <v>-5.712277983155563</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.54026010386605</v>
+        <v>1.538033417000627</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307675</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.523499602858911</v>
+        <v>-5.529066320022468</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.615975718583334</v>
+        <v>1.613749031717911</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863556</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.45177815584506</v>
+        <v>-5.457344873008617</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.627608703468252</v>
+        <v>1.625382016602829</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49132,16 +49132,16 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394118</v>
+        <v>3.723789705394115</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.429405130237354</v>
+        <v>-5.434971847400911</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.583473659632506</v>
+        <v>1.581246972767083</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456737</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.462421426148099</v>
+        <v>-5.467988143311656</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.755465346153563</v>
+        <v>1.75323865928814</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883687</v>
+        <v>3.713762536883683</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.45089379049849</v>
+        <v>-5.456460507662047</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.751997626241656</v>
+        <v>1.749770939376233</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49201,16 +49201,16 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236308</v>
+        <v>3.717150699236305</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.548235291840859</v>
+        <v>-5.553802009004416</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.716729138226496</v>
+        <v>1.714502451361074</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49224,16 +49224,16 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427695</v>
+        <v>3.705201079427692</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.634091321180826</v>
+        <v>-5.639658038344383</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.683637808683348</v>
+        <v>1.681411121817925</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49247,16 +49247,16 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610386</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.642928118596945</v>
+        <v>-5.648494835760502</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.662522291537402</v>
+        <v>1.660295604671979</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
@@ -49270,16 +49270,16 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667464</v>
+        <v>3.715544411667461</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.734310681162404</v>
+        <v>-5.739877398325961</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.636133777556268</v>
+        <v>1.633907090690845</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
@@ -49293,16 +49293,16 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889202</v>
+        <v>3.673978374889198</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.722603963175398</v>
+        <v>-5.728170680338954</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.742944722575339</v>
+        <v>1.740718035709916</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
@@ -49316,16 +49316,16 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409577</v>
+        <v>3.682476099409573</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.793516036917675</v>
+        <v>-5.799082754081232</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.717612231809833</v>
+        <v>1.71538554494441</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452576</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.803832135084027</v>
+        <v>-5.809398852247583</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.714304618275557</v>
+        <v>1.712077931410134</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5337776836251679</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.358403115201752</v>
+        <v>4.356460506798015</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762297</v>
+        <v>3.623960959762294</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.803738167066654</v>
+        <v>-5.809304884230211</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.713520872394595</v>
+        <v>1.711294185529173</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.357803698922233</v>
+        <v>4.355861090518496</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884089</v>
+        <v>3.800870306884086</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.947339331090039</v>
+        <v>-5.952906048253596</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.650312392729595</v>
+        <v>1.648085705864172</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.352035684866586</v>
+        <v>4.35009307646285</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129653</v>
+        <v>3.671015692129649</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.946390907972001</v>
+        <v>-5.951957625135558</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.65069176197681</v>
+        <v>1.648465075111388</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.352035684866586</v>
+        <v>4.35009307646285</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052356</v>
+        <v>3.904173816052353</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.046660725931021</v>
+        <v>-6.052227443094578</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.623311442774294</v>
+        <v>1.621084755908871</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.364763292847678</v>
+        <v>4.362820684443942</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.7401796078135</v>
+        <v>3.740179607813497</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.04066847914221</v>
+        <v>-6.046235196305767</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.627654339914207</v>
+        <v>1.625427653048784</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.366709291272066</v>
+        <v>4.364766682868329</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537949</v>
+        <v>3.765050796537945</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.952110518011442</v>
+        <v>-5.957677235174999</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.656731660384283</v>
+        <v>1.65450497351886</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.360363427289835</v>
+        <v>4.358420818886098</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771821</v>
+        <v>3.758409170771817</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.934351440508368</v>
+        <v>-5.939918157671925</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.663143968824508</v>
+        <v>1.660917281959085</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5373852256453805</v>
+        <v>0.5341475449724858</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.359672104728831</v>
+        <v>4.357729496325094</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109727</v>
+        <v>3.801340597109723</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.8347212894593</v>
+        <v>-5.840288006622857</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.715778215152722</v>
+        <v>1.713551528287299</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.637015376694448</v>
+        <v>0.6337776960215533</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.432232381266858</v>
+        <v>4.430289772863121</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546844001</v>
+        <v>3.798465546843997</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.884120798148311</v>
+        <v>-5.889687515311868</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.885172677175844</v>
+        <v>1.882945990310421</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6472742101261927</v>
+        <v>0.644036529453298</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.627541946824631</v>
+        <v>4.625599338420894</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351865</v>
+        <v>3.772186508351862</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.677436324505935</v>
+        <v>-5.683003041669492</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.955035139735656</v>
+        <v>1.952808452870233</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8539586837685683</v>
+        <v>0.8507210030956737</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.738741304112919</v>
+        <v>4.736798695709182</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551275</v>
+        <v>3.763392838551272</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.711593219503461</v>
+        <v>-5.717159936667018</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.943373895390751</v>
+        <v>1.941147208525328</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7671372335548612</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.690592556042536</v>
+        <v>4.688649947638799</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041117</v>
+        <v>3.805590565041113</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.619003740442005</v>
+        <v>-5.624570457605562</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.333906801005001</v>
+        <v>2.331680114139578</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7703749142277558</v>
+        <v>0.7671372335548612</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.044089670032204</v>
+        <v>5.042147061628467</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497408</v>
+        <v>3.832164354497404</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.69216434421515</v>
+        <v>-5.697731061378707</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.309205671062847</v>
+        <v>2.306978984197424</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7391160335206182</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.031840061578762</v>
+        <v>5.029897453175025</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492302</v>
+        <v>3.858310890492298</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.639948034418808</v>
+        <v>-5.645514751582365</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.379922136304911</v>
+        <v>2.377695449439488</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7423537141935128</v>
+        <v>0.7391160335206182</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.081670002902289</v>
+        <v>5.079727394498553</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436483</v>
+        <v>3.844935596436479</v>
       </c>
       <c r="C2093" t="n">
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.587440706908313</v>
+        <v>-5.59300742407187</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.40973903751912</v>
+        <v>2.407512350653697</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.7916233610311131</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.121988369618597</v>
+        <v>5.12004576121486</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039493</v>
+        <v>3.848376866039489</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.602196031108454</v>
+        <v>-5.607762748272011</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.39947449187826</v>
+        <v>2.397247805012838</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7948610417040077</v>
+        <v>0.7916233610311131</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.117625953657794</v>
+        <v>5.115683345254057</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524487</v>
+        <v>3.868153115524484</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.552731407738542</v>
+        <v>-5.558298124902099</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.410184844642505</v>
+        <v>2.407958157777082</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8443256650739194</v>
+        <v>0.8410879844010247</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.138229231096021</v>
+        <v>5.136286622692285</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867961</v>
+        <v>3.849040239867957</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.389623415584927</v>
+        <v>-5.395190132748484</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.471835709218886</v>
+        <v>2.469609022353463</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.007433657227535</v>
+        <v>1.00419597655464</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.232501694103124</v>
+        <v>5.230559085699388</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232976</v>
+        <v>3.870204928232972</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.368980324783699</v>
+        <v>-5.374547041947256</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.489139982230505</v>
+        <v>2.486913295365082</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.007433657227535</v>
+        <v>1.00419597655464</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.241548730794253</v>
+        <v>5.239606122390516</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.85553443717968</v>
+        <v>3.855534437179676</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.431688241258257</v>
+        <v>-5.437254958421814</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.464914280626803</v>
+        <v>2.46268759376138</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9414880600800822</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.20478144589564</v>
+        <v>5.202838837491903</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967727</v>
+        <v>3.884687848967723</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.383680117414564</v>
+        <v>-5.389246834578121</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.447026946954633</v>
+        <v>2.44480026008921</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9447257407529769</v>
+        <v>0.9414880600800822</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.167690862685992</v>
+        <v>5.165748254282255</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018618</v>
+        <v>3.895362357018614</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.233562062192667</v>
+        <v>-5.239128779356224</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.511006422601342</v>
+        <v>2.508779735735919</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.094843795974874</v>
+        <v>1.091606115301979</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.261693949377081</v>
+        <v>5.259751340973343</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075141</v>
+        <v>3.891610981075138</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.139004550819307</v>
+        <v>-5.144571267982864</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.543728519757723</v>
+        <v>2.5415018328923</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.094843795974874</v>
+        <v>1.091606115301979</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.256593041984118</v>
+        <v>5.25465043358038</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435451</v>
+        <v>3.872432493435448</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.02083117280138</v>
+        <v>-5.026397889964937</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.586351780353989</v>
+        <v>2.584125093488566</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.213017173992801</v>
+        <v>1.209779493319906</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.322850978183969</v>
+        <v>5.320908369780232</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.85957172391774</v>
+        <v>3.859571723917736</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.931984055941882</v>
+        <v>-4.937550773105439</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.650979219960815</v>
+        <v>2.648752533095392</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.301864290852299</v>
+        <v>1.298626610179404</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.405247841162694</v>
+        <v>5.403305232758957</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013646</v>
+        <v>3.828006274013642</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.904935018248628</v>
+        <v>-4.910501735412185</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.655359058049294</v>
+        <v>2.653132371183871</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.328913328545553</v>
+        <v>1.325675647872658</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.415037486789824</v>
+        <v>5.413094878386087</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263776</v>
+        <v>3.823987445263772</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.910968298435399</v>
+        <v>-4.916535015598956</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.652945745974586</v>
+        <v>2.650719059109163</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.328913328545553</v>
+        <v>1.325675647872658</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.415037486789824</v>
+        <v>5.413094878386087</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.81565720317085</v>
+        <v>3.815657203170846</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.96282007400856</v>
+        <v>-4.968386791172117</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.635843202887734</v>
+        <v>2.633616516022311</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.277061552972391</v>
+        <v>1.273823872299496</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.38756458858834</v>
+        <v>5.385621980184602</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431413</v>
+        <v>3.83058698643141</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.989877520140387</v>
+        <v>-4.995444237303944</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.58851197161884</v>
+        <v>2.586285284753417</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.277061552972391</v>
+        <v>1.273823872299496</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.351056335772176</v>
+        <v>5.349113727368439</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.83085645723246</v>
+        <v>3.830856457232456</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.063158871994262</v>
+        <v>-5.068725589157819</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.560607380624481</v>
+        <v>2.558380693759058</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.26315013084118</v>
+        <v>1.259912450168285</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.344117432240641</v>
+        <v>5.342174823836904</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.7848994180852</v>
+        <v>3.907285875710496</v>
       </c>
       <c r="C2109" t="n">
         <v>4.604467567238743</v>
       </c>
       <c r="D2109" t="n">
-        <v>-4.960370890690502</v>
+        <v>-5.071224279789984</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.619962786648795</v>
+        <v>2.575621431009002</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.26315013084118</v>
+        <v>1.259912450168285</v>
       </c>
       <c r="G2109" t="n">
-        <v>5.362357645743451</v>
+        <v>5.360415037339714</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241007.xlsx
+++ b/tame_output/ON/bt/strategyON_20241007.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.6%</t>
+          <t>423.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.7%</t>
+          <t>-660.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-118.7%</t>
+          <t>-115.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-203.6%</t>
+          <t>-204.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.0%</t>
+          <t>-95.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>102.8%</t>
+          <t>103.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
     </row>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.112505805576032</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.111029846703034</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.107794290680233</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.174500250270737</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.64075008781467</v>
       </c>
       <c r="C2016" t="n">
         <v>3.314811969272584</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237098</v>
+        <v>3.668289004237099</v>
       </c>
       <c r="C2017" t="n">
         <v>3.383792238418224</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609757</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
         <v>3.381713929593758</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67402853597316</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.382924464112702</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916205</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.382124059076213</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.544328115775257</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071556</v>
       </c>
       <c r="C2024" t="n">
         <v>3.539174753739071</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868153</v>
+        <v>3.750044015868154</v>
       </c>
       <c r="C2025" t="n">
         <v>3.549404171307562</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332699</v>
+        <v>3.783632867332701</v>
       </c>
       <c r="C2026" t="n">
         <v>3.558329809763465</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231816</v>
+        <v>3.798296784231818</v>
       </c>
       <c r="C2027" t="n">
         <v>3.55048269700764</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818525</v>
       </c>
       <c r="C2028" t="n">
         <v>3.554732707729614</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051791</v>
       </c>
       <c r="C2029" t="n">
         <v>3.56199359061215</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679629</v>
       </c>
       <c r="C2030" t="n">
         <v>3.562964768364861</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
         <v>3.563807672744617</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969548</v>
       </c>
       <c r="C2032" t="n">
         <v>3.582845771618762</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700484</v>
       </c>
       <c r="C2033" t="n">
         <v>3.399029767742697</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077644</v>
+        <v>3.804688961077647</v>
       </c>
       <c r="C2034" t="n">
         <v>3.402531811816661</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833464</v>
+        <v>3.775028860833467</v>
       </c>
       <c r="C2035" t="n">
         <v>3.386958630892743</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077632</v>
       </c>
       <c r="C2036" t="n">
         <v>3.386146341329173</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147914</v>
       </c>
       <c r="C2037" t="n">
         <v>3.396015120454245</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.83441549373529</v>
       </c>
       <c r="C2038" t="n">
         <v>3.466852126230671</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496559</v>
       </c>
       <c r="C2039" t="n">
         <v>3.463721137048969</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108862</v>
+        <v>3.815643212108865</v>
       </c>
       <c r="C2040" t="n">
         <v>3.468252031988361</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121474</v>
+        <v>3.807356168121477</v>
       </c>
       <c r="C2041" t="n">
         <v>3.468381285466904</v>
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906087</v>
+        <v>3.77523303390609</v>
       </c>
       <c r="C2042" t="n">
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.059031748287619</v>
+        <v>-5.061076229074324</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.424249007575705</v>
+        <v>1.423431215261024</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.5717206765542611</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.791250537137057</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912991</v>
+        <v>3.785761685912995</v>
       </c>
       <c r="C2043" t="n">
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.003701160385857</v>
+        <v>-5.005745641172561</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.481348179348469</v>
+        <v>1.480530387033787</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.6270512644560232</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.859415826490173</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539901</v>
+        <v>3.743767956539904</v>
       </c>
       <c r="C2044" t="n">
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.991647033472894</v>
+        <v>-4.993691514259599</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.479856398015092</v>
+        <v>1.47903860570041</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.639105391368986</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.844272441699299</v>
+        <v>3.860334870539389</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811016</v>
+        <v>3.72501084481102</v>
       </c>
       <c r="C2045" t="n">
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.069002523600863</v>
+        <v>-5.071047004387568</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.45079483214804</v>
+        <v>1.449977039833358</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5349791865075343</v>
+        <v>0.5617499012410166</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.799739777806653</v>
+        <v>3.815802206646743</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382927</v>
+        <v>3.61232244438293</v>
       </c>
       <c r="C2046" t="n">
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.000953960909333</v>
+        <v>-5.002998441696038</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.490865283102534</v>
+        <v>1.490047490787852</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6297984639325465</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.853419941299454</v>
+        <v>3.869482370139543</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013434</v>
+        <v>3.645256780013437</v>
       </c>
       <c r="C2047" t="n">
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.232554354078834</v>
+        <v>-5.234598834865539</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.418427796008328</v>
+        <v>1.417610003693647</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6297984639325465</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.873622611473048</v>
+        <v>3.889685040313137</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498973</v>
       </c>
       <c r="C2048" t="n">
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.282605899608054</v>
+        <v>-5.284650380394758</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.382013413863522</v>
+        <v>1.38119562154884</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6297984639325465</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.85722884753993</v>
+        <v>3.873291276380019</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800102</v>
       </c>
       <c r="C2049" t="n">
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.457712732184499</v>
+        <v>-5.459757212971203</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.272222594426411</v>
+        <v>1.271404802111729</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030277491990641</v>
+        <v>0.6297984639325465</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.817480761133397</v>
+        <v>3.833543189973486</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660855</v>
       </c>
       <c r="C2050" t="n">
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.261612578753976</v>
+        <v>-5.26365705954068</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.35768527479556</v>
+        <v>1.356867482480878</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.799127902629587</v>
+        <v>0.8258986173630694</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.94216347218865</v>
+        <v>3.958225901028739</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.730570473395092</v>
       </c>
       <c r="C2051" t="n">
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.108587186640691</v>
+        <v>-5.110631667427396</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.518066431213778</v>
+        <v>1.517248638899097</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.9789240094763535</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.133149707029525</v>
+        <v>4.149212135869615</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791154</v>
       </c>
       <c r="C2052" t="n">
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.136894500513962</v>
+        <v>-5.138938981300666</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.694209730572763</v>
+        <v>1.693391938258081</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9521532947428711</v>
+        <v>0.9789240094763535</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.320615931937818</v>
+        <v>4.336678360777907</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620436</v>
+        <v>3.69911561562044</v>
       </c>
       <c r="C2053" t="n">
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.303487725627484</v>
+        <v>-5.305532206414188</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.596975391881437</v>
+        <v>1.596157599566755</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8123307843628311</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.190062948223787</v>
+        <v>4.206125377063876</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285653</v>
       </c>
       <c r="C2054" t="n">
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.280451932265918</v>
+        <v>-5.282496413052622</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.609866111887781</v>
+        <v>1.609048319573099</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8123307843628311</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.193739350885505</v>
+        <v>4.209801779725594</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399474</v>
       </c>
       <c r="C2055" t="n">
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.251205951810221</v>
+        <v>-5.253250432596926</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.619182559193554</v>
+        <v>1.618364766878873</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7855600696293488</v>
+        <v>0.8123307843628311</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.191357406009</v>
+        <v>4.207419834849089</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256377</v>
       </c>
       <c r="C2056" t="n">
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.358131499688072</v>
+        <v>-5.360175980474777</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.573705579200049</v>
+        <v>1.572887786885367</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786345217514974</v>
+        <v>0.7054052364849798</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.124495316439925</v>
+        <v>4.140557745280013</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701007</v>
       </c>
       <c r="C2057" t="n">
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.503150058195321</v>
+        <v>-5.505194538982026</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.517126957940384</v>
+        <v>1.516309165625702</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336159632442489</v>
+        <v>0.5603866779777312</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.038912983478809</v>
+        <v>4.054975412318899</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687019</v>
       </c>
       <c r="C2058" t="n">
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.621491823980039</v>
+        <v>-5.623536304766743</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.56972149088425</v>
+        <v>1.568903698569568</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5710727165406213</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.145255845874297</v>
+        <v>4.161318274714386</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790808</v>
+        <v>3.714879051790811</v>
       </c>
       <c r="C2059" t="n">
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.672902246300747</v>
+        <v>-5.674946727087451</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.546943019081906</v>
+        <v>1.546125226767224</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5710727165406213</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.143041543000235</v>
+        <v>4.159103971840325</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437337</v>
+        <v>3.70475794943734</v>
       </c>
       <c r="C2060" t="n">
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.752321697508498</v>
+        <v>-5.754366178295203</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.515078366673094</v>
+        <v>1.514260574358413</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5710727165406213</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.142944671074525</v>
+        <v>4.159007099914614</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298405</v>
+        <v>3.736804952298408</v>
       </c>
       <c r="C2061" t="n">
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.847784695425716</v>
+        <v>-5.84982917621242</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.47688706106425</v>
+        <v>1.476069268749569</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443020018071389</v>
+        <v>0.5710727165406213</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.142938564632567</v>
+        <v>4.159000993472657</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218008</v>
+        <v>3.715372960218011</v>
       </c>
       <c r="C2062" t="n">
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.783408784575001</v>
+        <v>-5.785453265361705</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.500733821967147</v>
+        <v>1.499916029652465</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6354486273913365</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.179660507705607</v>
+        <v>4.195722936545697</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353543</v>
+        <v>3.736089413353547</v>
       </c>
       <c r="C2063" t="n">
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.838777946707195</v>
+        <v>-5.840822427493899</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.484319974861996</v>
+        <v>1.483502182547314</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6086779126578541</v>
+        <v>0.6354486273913365</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.185394325453334</v>
+        <v>4.201456754293424</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113286</v>
+        <v>3.73682287011329</v>
       </c>
       <c r="C2064" t="n">
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.856996413704803</v>
+        <v>-5.859040894491508</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.476570951405885</v>
+        <v>1.475753159091203</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6103421901354943</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.169868826442761</v>
+        <v>4.18593125528285</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113695</v>
+        <v>3.790272500113699</v>
       </c>
       <c r="C2065" t="n">
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.818312978360873</v>
+        <v>-5.820357459147577</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.511918718393776</v>
+        <v>1.511100926079094</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6103421901354943</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.18974321929308</v>
+        <v>4.205805648133169</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.712277983155563</v>
+        <v>-5.714322463942268</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.538033417000627</v>
+        <v>1.537215624685946</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6103421901354943</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.173443919817807</v>
+        <v>4.189506348657897</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.794705093307675</v>
       </c>
       <c r="C2067" t="n">
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.529066320022468</v>
+        <v>-5.531110800809173</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.613749031717911</v>
+        <v>1.61293123940323</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5835714754020119</v>
+        <v>0.6103421901354943</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.175874869281854</v>
+        <v>4.191937298121942</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863556</v>
       </c>
       <c r="C2068" t="n">
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.457344873008617</v>
+        <v>-5.459389353795322</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.625382016602829</v>
+        <v>1.624564224288147</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6552929224158626</v>
+        <v>0.6820636371493449</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.201852143569541</v>
+        <v>4.21791457240963</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394115</v>
+        <v>3.723789705394118</v>
       </c>
       <c r="C2069" t="n">
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.434971847400911</v>
+        <v>-5.437016328187616</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.581246972767083</v>
+        <v>1.580429180452401</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665486735287641</v>
+        <v>0.6933193882622465</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.155521340158454</v>
+        <v>4.171583768998543</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456736</v>
       </c>
       <c r="C2070" t="n">
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.467988143311656</v>
+        <v>-5.47003262409836</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.75323865928814</v>
+        <v>1.752420866973459</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971112968620125</v>
+        <v>0.6238820115954948</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.299057119043757</v>
+        <v>4.315119547883847</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883683</v>
+        <v>3.713762536883687</v>
       </c>
       <c r="C2071" t="n">
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.456460507662047</v>
+        <v>-5.458504988448752</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.749770939376233</v>
+        <v>1.748953147061551</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561119550633749</v>
+        <v>0.6828826697968573</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.326378739792824</v>
+        <v>4.342441168632914</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236305</v>
+        <v>3.717150699236308</v>
       </c>
       <c r="C2072" t="n">
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.553802009004416</v>
+        <v>-5.55584648979112</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.714502451361074</v>
+        <v>1.713684659046392</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6116917728978866</v>
+        <v>0.6384624876313689</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.303394743015319</v>
+        <v>4.319457171855409</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427692</v>
+        <v>3.705201079427695</v>
       </c>
       <c r="C2073" t="n">
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.639658038344383</v>
+        <v>-5.641702519131087</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.681411121817925</v>
+        <v>1.680593329503244</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693157036717515</v>
+        <v>0.5960864184052339</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.279220183672477</v>
+        <v>4.295282612512566</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.691835499610386</v>
       </c>
       <c r="C2074" t="n">
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.648494835760502</v>
+        <v>-5.650539316547206</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.660295604671979</v>
+        <v>1.659477812357298</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5618735310304008</v>
+        <v>0.5886442457638832</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.257174081908168</v>
+        <v>4.273236510748258</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667461</v>
+        <v>3.715544411667464</v>
       </c>
       <c r="C2075" t="n">
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.739877398325961</v>
+        <v>-5.741921879112665</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.633907090690845</v>
+        <v>1.633089298376164</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253086463110561</v>
+        <v>0.5520793610445385</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.245399662121611</v>
+        <v>4.2614620909617</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889198</v>
+        <v>3.673978374889202</v>
       </c>
       <c r="C2076" t="n">
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.728170680338954</v>
+        <v>-5.730215161125659</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.740718035709916</v>
+        <v>1.739900243395234</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5637860790315449</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.354551950738083</v>
+        <v>4.370614379578172</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409573</v>
+        <v>3.682476099409577</v>
       </c>
       <c r="C2077" t="n">
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.799082754081232</v>
+        <v>-5.801127234867936</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.71538554494441</v>
+        <v>1.714567752629728</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370153642980625</v>
+        <v>0.5637860790315449</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.357584289469488</v>
+        <v>4.373646718309577</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.672895177452576</v>
       </c>
       <c r="C2078" t="n">
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.809398852247583</v>
+        <v>-5.811443333034288</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.712077931410134</v>
+        <v>1.711260139095452</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5337776836251679</v>
+        <v>0.5637860790315449</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.356460506798015</v>
+        <v>4.374465544041842</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762294</v>
+        <v>3.623960959762297</v>
       </c>
       <c r="C2079" t="n">
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.809304884230211</v>
+        <v>-5.811349365016915</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.711294185529173</v>
+        <v>1.710476393214491</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.355861090518496</v>
+        <v>4.373866127762322</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884086</v>
+        <v>3.800870306884089</v>
       </c>
       <c r="C2080" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.952906048253596</v>
+        <v>-5.954950529040301</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.648085705864172</v>
+        <v>1.647267913549491</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.35009307646285</v>
+        <v>4.368098113706676</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129649</v>
+        <v>3.671015692129653</v>
       </c>
       <c r="C2081" t="n">
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.951957625135558</v>
+        <v>-5.954002105922262</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.648465075111388</v>
+        <v>1.647647282796706</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.35009307646285</v>
+        <v>4.368098113706676</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052353</v>
+        <v>3.904173816052356</v>
       </c>
       <c r="C2082" t="n">
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.052227443094578</v>
+        <v>-6.054271923881283</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.621084755908871</v>
+        <v>1.62026696359419</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.362820684443942</v>
+        <v>4.380825721687768</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.740179607813497</v>
+        <v>3.7401796078135</v>
       </c>
       <c r="C2083" t="n">
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.046235196305767</v>
+        <v>-6.048279677092471</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.625427653048784</v>
+        <v>1.624609860734102</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.364766682868329</v>
+        <v>4.382771720112156</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537945</v>
+        <v>3.765050796537949</v>
       </c>
       <c r="C2084" t="n">
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.957677235174999</v>
+        <v>-5.959721715961703</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.65450497351886</v>
+        <v>1.653687181204178</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.358420818886098</v>
+        <v>4.376425856129925</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771817</v>
+        <v>3.758409170771821</v>
       </c>
       <c r="C2085" t="n">
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.939918157671925</v>
+        <v>-5.941962638458629</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.660917281959085</v>
+        <v>1.660099489644403</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5341475449724858</v>
+        <v>0.5641559403788629</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.357729496325094</v>
+        <v>4.37573453356892</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109723</v>
+        <v>3.801340597109727</v>
       </c>
       <c r="C2086" t="n">
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.840288006622857</v>
+        <v>-5.842332487409561</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.713551528287299</v>
+        <v>1.712733735972617</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6337776960215533</v>
+        <v>0.6637860914279303</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.430289772863121</v>
+        <v>4.448294810106947</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546843997</v>
+        <v>3.798465546844001</v>
       </c>
       <c r="C2087" t="n">
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.889687515311868</v>
+        <v>-5.891731996098573</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.882945990310421</v>
+        <v>1.882128197995739</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.644036529453298</v>
+        <v>0.674044924859675</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.625599338420894</v>
+        <v>4.643604375664721</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351862</v>
+        <v>3.772186508351865</v>
       </c>
       <c r="C2088" t="n">
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.683003041669492</v>
+        <v>-5.685047522456196</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.952808452870233</v>
+        <v>1.951990660555551</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8507210030956737</v>
+        <v>0.8807293985020507</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.736798695709182</v>
+        <v>4.754803732953008</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551272</v>
+        <v>3.763392838551275</v>
       </c>
       <c r="C2089" t="n">
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.717159936667018</v>
+        <v>-5.719204417453723</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.941147208525328</v>
+        <v>1.940329416210646</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7671372335548612</v>
+        <v>0.7971456289612382</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.688649947638799</v>
+        <v>4.706654984882626</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041113</v>
+        <v>3.805590565041117</v>
       </c>
       <c r="C2090" t="n">
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.624570457605562</v>
+        <v>-5.626614938392266</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.331680114139578</v>
+        <v>2.330862321824896</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7671372335548612</v>
+        <v>0.7971456289612382</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.042147061628467</v>
+        <v>5.060152098872293</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497404</v>
+        <v>3.832164354497408</v>
       </c>
       <c r="C2091" t="n">
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.697731061378707</v>
+        <v>-5.699775542165411</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.306978984197424</v>
+        <v>2.306161191882742</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7391160335206182</v>
+        <v>0.7691244289269952</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.029897453175025</v>
+        <v>5.047902490418851</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492298</v>
+        <v>3.858310890492302</v>
       </c>
       <c r="C2092" t="n">
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.645514751582365</v>
+        <v>-5.647559232369069</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.377695449439488</v>
+        <v>2.376877657124806</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7391160335206182</v>
+        <v>0.7691244289269952</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.079727394498553</v>
+        <v>5.097732431742378</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436479</v>
+        <v>3.844935596436483</v>
       </c>
       <c r="C2093" t="n">
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.59300742407187</v>
+        <v>-5.595051904858575</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.407512350653697</v>
+        <v>2.406694558339015</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7916233610311131</v>
+        <v>0.8216317564374901</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.12004576121486</v>
+        <v>5.138050798458687</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039489</v>
+        <v>3.848376866039493</v>
       </c>
       <c r="C2094" t="n">
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.607762748272011</v>
+        <v>-5.609807229058715</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.397247805012838</v>
+        <v>2.396430012698156</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7916233610311131</v>
+        <v>0.8216317564374901</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.115683345254057</v>
+        <v>5.133688382497883</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524484</v>
+        <v>3.868153115524487</v>
       </c>
       <c r="C2095" t="n">
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.558298124902099</v>
+        <v>-5.560342605688803</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.407958157777082</v>
+        <v>2.4071403654624</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8410879844010247</v>
+        <v>0.8710963798074017</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.136286622692285</v>
+        <v>5.154291659936111</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867957</v>
+        <v>3.849040239867961</v>
       </c>
       <c r="C2096" t="n">
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.395190132748484</v>
+        <v>-5.397234613535188</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.469609022353463</v>
+        <v>2.468791230038781</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.00419597655464</v>
+        <v>1.034204371961017</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.230559085699388</v>
+        <v>5.248564122943214</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232972</v>
+        <v>3.870204928232976</v>
       </c>
       <c r="C2097" t="n">
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.374547041947256</v>
+        <v>-5.37659152273396</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.486913295365082</v>
+        <v>2.486095503050401</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.00419597655464</v>
+        <v>1.034204371961017</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.239606122390516</v>
+        <v>5.257611159634342</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.855534437179676</v>
+        <v>3.85553443717968</v>
       </c>
       <c r="C2098" t="n">
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.437254958421814</v>
+        <v>-5.439299439208519</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.46268759376138</v>
+        <v>2.461869801446699</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9414880600800822</v>
+        <v>0.9714964554864592</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.202838837491903</v>
+        <v>5.22084387473573</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967723</v>
+        <v>3.884687848967727</v>
       </c>
       <c r="C2099" t="n">
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.389246834578121</v>
+        <v>-5.391291315364826</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.44480026008921</v>
+        <v>2.443982467774528</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9414880600800822</v>
+        <v>0.9714964554864592</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.165748254282255</v>
+        <v>5.183753291526082</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018614</v>
+        <v>3.895362357018618</v>
       </c>
       <c r="C2100" t="n">
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.239128779356224</v>
+        <v>-5.241173260142928</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.508779735735919</v>
+        <v>2.507961943421237</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.091606115301979</v>
+        <v>1.121614510708356</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.259751340973343</v>
+        <v>5.27775637821717</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075138</v>
+        <v>3.891610981075141</v>
       </c>
       <c r="C2101" t="n">
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.144571267982864</v>
+        <v>-5.146615748769569</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.5415018328923</v>
+        <v>2.540684040577618</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.091606115301979</v>
+        <v>1.121614510708356</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.25465043358038</v>
+        <v>5.272655470824207</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435448</v>
+        <v>3.872432493435451</v>
       </c>
       <c r="C2102" t="n">
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.026397889964937</v>
+        <v>-5.028442370751641</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.584125093488566</v>
+        <v>2.583307301173885</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.209779493319906</v>
+        <v>1.239787888726283</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.320908369780232</v>
+        <v>5.338913407024059</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.859571723917736</v>
+        <v>3.85957172391774</v>
       </c>
       <c r="C2103" t="n">
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.937550773105439</v>
+        <v>-4.939595253892143</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.648752533095392</v>
+        <v>2.647934740780711</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.298626610179404</v>
+        <v>1.328635005585781</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.403305232758957</v>
+        <v>5.421310270002784</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013642</v>
+        <v>3.828006274013646</v>
       </c>
       <c r="C2104" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.910501735412185</v>
+        <v>-4.91254621619889</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.653132371183871</v>
+        <v>2.652314578869189</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.325675647872658</v>
+        <v>1.355684043279035</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.413094878386087</v>
+        <v>5.431099915629913</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263772</v>
+        <v>3.823987445263776</v>
       </c>
       <c r="C2105" t="n">
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.916535015598956</v>
+        <v>-4.91857949638566</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.650719059109163</v>
+        <v>2.649901266794481</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.325675647872658</v>
+        <v>1.355684043279035</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.413094878386087</v>
+        <v>5.431099915629913</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.815657203170846</v>
+        <v>3.81565720317085</v>
       </c>
       <c r="C2106" t="n">
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.968386791172117</v>
+        <v>-4.970431271958821</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.633616516022311</v>
+        <v>2.632798723707629</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.273823872299496</v>
+        <v>1.303832267705873</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.385621980184602</v>
+        <v>5.403627017428429</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.83058698643141</v>
+        <v>3.830586986431413</v>
       </c>
       <c r="C2107" t="n">
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.995444237303944</v>
+        <v>-4.997488718090648</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.586285284753417</v>
+        <v>2.585467492438735</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.273823872299496</v>
+        <v>1.303832267705873</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.349113727368439</v>
+        <v>5.367118764612266</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.830856457232456</v>
+        <v>3.83085645723246</v>
       </c>
       <c r="C2108" t="n">
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.068725589157819</v>
+        <v>-5.070770069944524</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.558380693759058</v>
+        <v>2.557562901444376</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.259912450168285</v>
+        <v>1.289920845574662</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.342174823836904</v>
+        <v>5.360179861080731</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.907285875710496</v>
+        <v>3.786339171305457</v>
       </c>
       <c r="C2109" t="n">
         <v>4.604467567238743</v>
       </c>
       <c r="D2109" t="n">
-        <v>-5.071224279789984</v>
+        <v>-4.990126659271492</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.575621431009002</v>
+        <v>2.608060479216399</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.259912450168285</v>
+        <v>1.289920845574662</v>
       </c>
       <c r="G2109" t="n">
-        <v>5.360415037339714</v>
+        <v>5.37842007458354</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241007.xlsx
+++ b/tame_output/ON/bt/strategyON_20241007.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.7%</t>
+          <t>424.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.6%</t>
+          <t>-659.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-115.4%</t>
+          <t>-114.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.4%</t>
+          <t>-204.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.0%</t>
+          <t>-96.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.0%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.061076229074324</v>
+        <v>-5.059031748287619</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.423431215261024</v>
+        <v>1.424249007575705</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5717206765542611</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.791250537137057</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.005745641172561</v>
+        <v>-5.003701160385857</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.480530387033787</v>
+        <v>1.481348179348469</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6270512644560232</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.859415826490173</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.993691514259599</v>
+        <v>-4.978338052546152</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.47903860570041</v>
+        <v>1.485179990385788</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.639105391368986</v>
+        <v>0.6256436575622454</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.860334870539389</v>
+        <v>3.852257830255344</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.071047004387568</v>
+        <v>-5.055693542674121</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.449977039833358</v>
+        <v>1.456118424518737</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5617499012410166</v>
+        <v>0.548288167434276</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.815802206646743</v>
+        <v>3.807725166362698</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-5.002998441696038</v>
+        <v>-4.987644979982591</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.490047490787852</v>
+        <v>1.496188875473231</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6297984639325465</v>
+        <v>0.6163367301258058</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.869482370139543</v>
+        <v>3.861405329855498</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.234598834865539</v>
+        <v>-5.219245373152092</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.417610003693647</v>
+        <v>1.423751388379025</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6297984639325465</v>
+        <v>0.6163367301258058</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.889685040313137</v>
+        <v>3.881608000029093</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.284650380394758</v>
+        <v>-5.269296918681311</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.38119562154884</v>
+        <v>1.387337006234219</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6297984639325465</v>
+        <v>0.6163367301258058</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.873291276380019</v>
+        <v>3.865214236095975</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.459757212971203</v>
+        <v>-5.444403751257756</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.271404802111729</v>
+        <v>1.277546186797108</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6297984639325465</v>
+        <v>0.6163367301258058</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.833543189973486</v>
+        <v>3.825466149689441</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.26365705954068</v>
+        <v>-5.248303597827233</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.356867482480878</v>
+        <v>1.363008867166257</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8258986173630694</v>
+        <v>0.8124368835563287</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.958225901028739</v>
+        <v>3.950148860744696</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.110631667427396</v>
+        <v>-5.095278205713949</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.517248638899097</v>
+        <v>1.523390023584475</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9789240094763535</v>
+        <v>0.9654622756696128</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.149212135869615</v>
+        <v>4.14113509558557</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.138938981300666</v>
+        <v>-5.123585519587219</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.693391938258081</v>
+        <v>1.69953332294346</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9789240094763535</v>
+        <v>0.9654622756696128</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.336678360777907</v>
+        <v>4.328601320493862</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.305532206414188</v>
+        <v>-5.290178744700741</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.596157599566755</v>
+        <v>1.602298984252134</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8123307843628311</v>
+        <v>0.7988690505560905</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.206125377063876</v>
+        <v>4.198048336779832</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.282496413052622</v>
+        <v>-5.267142951339175</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.609048319573099</v>
+        <v>1.615189704258478</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8123307843628311</v>
+        <v>0.7988690505560905</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.209801779725594</v>
+        <v>4.201724739441549</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.253250432596926</v>
+        <v>-5.237896970883479</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.618364766878873</v>
+        <v>1.624506151564252</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8123307843628311</v>
+        <v>0.7988690505560905</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.207419834849089</v>
+        <v>4.199342794565045</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.360175980474777</v>
+        <v>-5.34482251876133</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.572887786885367</v>
+        <v>1.579029171570746</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7054052364849798</v>
+        <v>0.6919435026782391</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.140557745280013</v>
+        <v>4.132480704995969</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.505194538982026</v>
+        <v>-5.489841077268578</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.516309165625702</v>
+        <v>1.522450550311081</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5603866779777312</v>
+        <v>0.5469249441709906</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.054975412318899</v>
+        <v>4.046898372034854</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.623536304766743</v>
+        <v>-5.608182843053296</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.568903698569568</v>
+        <v>1.575045083254947</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5710727165406213</v>
+        <v>0.5576109827338807</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.161318274714386</v>
+        <v>4.153241234430341</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.674946727087451</v>
+        <v>-5.659593265374004</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.546125226767224</v>
+        <v>1.552266611452603</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5710727165406213</v>
+        <v>0.5576109827338807</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.159103971840325</v>
+        <v>4.15102693155628</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.754366178295203</v>
+        <v>-5.739012716581755</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.514260574358413</v>
+        <v>1.520401959043792</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5710727165406213</v>
+        <v>0.5576109827338807</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.159007099914614</v>
+        <v>4.15093005963057</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.84982917621242</v>
+        <v>-5.834475714498973</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.476069268749569</v>
+        <v>1.482210653434947</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5710727165406213</v>
+        <v>0.5576109827338807</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.159000993472657</v>
+        <v>4.150923953188612</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.785453265361705</v>
+        <v>-5.770099803648258</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.499916029652465</v>
+        <v>1.506057414337844</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6354486273913365</v>
+        <v>0.6219868935845958</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.195722936545697</v>
+        <v>4.187645896261652</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.840822427493899</v>
+        <v>-5.825468965780452</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.483502182547314</v>
+        <v>1.489643567232693</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6354486273913365</v>
+        <v>0.6219868935845958</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.201456754293424</v>
+        <v>4.193379714009379</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.859040894491508</v>
+        <v>-5.843687432778061</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.475753159091203</v>
+        <v>1.481894543776582</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6103421901354943</v>
+        <v>0.5968804563287536</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.18593125528285</v>
+        <v>4.177854214998806</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.820357459147577</v>
+        <v>-5.80500399743413</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.511100926079094</v>
+        <v>1.517242310764473</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6103421901354943</v>
+        <v>0.5968804563287536</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.205805648133169</v>
+        <v>4.197728607849124</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.714322463942268</v>
+        <v>-5.698969002228821</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.537215624685946</v>
+        <v>1.543357009371324</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6103421901354943</v>
+        <v>0.5968804563287536</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.189506348657897</v>
+        <v>4.181429308373852</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.531110800809173</v>
+        <v>-5.515757339095726</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.61293123940323</v>
+        <v>1.619072624088608</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6103421901354943</v>
+        <v>0.5968804563287536</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.191937298121942</v>
+        <v>4.183860257837899</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.459389353795322</v>
+        <v>-5.444035892081875</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.624564224288147</v>
+        <v>1.630705608973526</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6820636371493449</v>
+        <v>0.6686019033426043</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.21791457240963</v>
+        <v>4.209837532125586</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.437016328187616</v>
+        <v>-5.421662866474168</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.580429180452401</v>
+        <v>1.58657056513778</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6933193882622465</v>
+        <v>0.6798576544555058</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.171583768998543</v>
+        <v>4.163506728714498</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.47003262409836</v>
+        <v>-5.454679162384913</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.752420866973459</v>
+        <v>1.758562251658837</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6238820115954948</v>
+        <v>0.6104202777887542</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.315119547883847</v>
+        <v>4.307042507599803</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.458504988448752</v>
+        <v>-5.443151526735305</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.748953147061551</v>
+        <v>1.75509453174693</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6828826697968573</v>
+        <v>0.6694209359901167</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.342441168632914</v>
+        <v>4.334364128348869</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.55584648979112</v>
+        <v>-5.540493028077673</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.713684659046392</v>
+        <v>1.719826043731771</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6384624876313689</v>
+        <v>0.6250007538246283</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.319457171855409</v>
+        <v>4.311380131571365</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.641702519131087</v>
+        <v>-5.62634905741764</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.680593329503244</v>
+        <v>1.686734714188622</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5960864184052339</v>
+        <v>0.5826246845984933</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.295282612512566</v>
+        <v>4.287205572228522</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.650539316547206</v>
+        <v>-5.635185854833759</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.659477812357298</v>
+        <v>1.665619197042676</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5886442457638832</v>
+        <v>0.5751825119571425</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.273236510748258</v>
+        <v>4.265159470464213</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.741921879112665</v>
+        <v>-5.726568417399218</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.633089298376164</v>
+        <v>1.639230683061542</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5520793610445385</v>
+        <v>0.5386176272377978</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.2614620909617</v>
+        <v>4.253385050677656</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.730215161125659</v>
+        <v>-5.714861699412212</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.739900243395234</v>
+        <v>1.746041628080613</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5637860790315449</v>
+        <v>0.5503243452248042</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.370614379578172</v>
+        <v>4.362537339294128</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.801127234867936</v>
+        <v>-5.785773773154489</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.714567752629728</v>
+        <v>1.720709137315107</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5637860790315449</v>
+        <v>0.5503243452248042</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.373646718309577</v>
+        <v>4.365569678025532</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.811443333034288</v>
+        <v>-5.796089871320841</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.711260139095452</v>
+        <v>1.717401523780831</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5637860790315449</v>
+        <v>0.5503243452248042</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.374465544041842</v>
+        <v>4.366388503757797</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.811349365016915</v>
+        <v>-5.795995903303468</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.710476393214491</v>
+        <v>1.71661777789987</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.373866127762322</v>
+        <v>4.365789087478277</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.954950529040301</v>
+        <v>-5.939597067326853</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.647267913549491</v>
+        <v>1.653409298234869</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.368098113706676</v>
+        <v>4.360021073422631</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.954002105922262</v>
+        <v>-5.938648644208815</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.647647282796706</v>
+        <v>1.653788667482085</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.368098113706676</v>
+        <v>4.360021073422631</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.04233215746045</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.054271923881283</v>
+        <v>-6.038918462167835</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.62026696359419</v>
+        <v>1.626408348279568</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.380825721687768</v>
+        <v>4.372748681403723</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.044278155884838</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.048279677092471</v>
+        <v>-6.032926215379024</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.624609860734102</v>
+        <v>1.630751245419481</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.382771720112156</v>
+        <v>4.374694679828111</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.037932291902607</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.959721715961703</v>
+        <v>-5.944368254248256</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.653687181204178</v>
+        <v>1.659828565889557</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.376425856129925</v>
+        <v>4.36834881584588</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.037240969341602</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.941962638458629</v>
+        <v>-5.926609176745182</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.660099489644403</v>
+        <v>1.666240874329782</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5641559403788629</v>
+        <v>0.5506942065721222</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.37573453356892</v>
+        <v>4.367657493284876</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.050023155250189</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.842332487409561</v>
+        <v>-5.826979025696114</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.712733735972617</v>
+        <v>1.718875120657996</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6637860914279303</v>
+        <v>0.6503243576211897</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.448294810106947</v>
+        <v>4.440217769822903</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.239177420748915</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.891731996098573</v>
+        <v>-5.876378534385125</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.882128197995739</v>
+        <v>1.888269582681118</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.674044924859675</v>
+        <v>0.6605831910529344</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.643604375664721</v>
+        <v>4.635527335380677</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.226366093851778</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.685047522456196</v>
+        <v>-5.669694060742749</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.951990660555551</v>
+        <v>1.958132045240931</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8807293985020507</v>
+        <v>0.86726766469531</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.754803732953008</v>
+        <v>4.746726692668964</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.228367607505882</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.719204417453723</v>
+        <v>-5.703850955740275</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.940329416210646</v>
+        <v>1.946470800896025</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7971456289612382</v>
+        <v>0.7836838951544975</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.706654984882626</v>
+        <v>4.698577944598581</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.58186472149555</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.626614938392266</v>
+        <v>-5.611261476678819</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.330862321824896</v>
+        <v>2.337003706510275</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7971456289612382</v>
+        <v>0.7836838951544975</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.060152098872293</v>
+        <v>5.052075058588248</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.586427833062654</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.699775542165411</v>
+        <v>-5.684422080451964</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.306161191882742</v>
+        <v>2.312302576568121</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7691244289269952</v>
+        <v>0.7556626951202545</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.047902490418851</v>
+        <v>5.039825450134807</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.636257774386181</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.647559232369069</v>
+        <v>-5.632205770655622</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.376877657124806</v>
+        <v>2.383019041810186</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7691244289269952</v>
+        <v>0.7556626951202545</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.097732431742378</v>
+        <v>5.089655391458335</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.645071744596192</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.595051904858575</v>
+        <v>-5.579698443145127</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.406694558339015</v>
+        <v>2.412835943024394</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8216317564374901</v>
+        <v>0.8081700226307494</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.138050798458687</v>
+        <v>5.129973758174643</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.640709328635389</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.609807229058715</v>
+        <v>-5.594453767345268</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.396430012698156</v>
+        <v>2.402571397383535</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8216317564374901</v>
+        <v>0.8081700226307494</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.133688382497883</v>
+        <v>5.12561134221384</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.631633832051669</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.560342605688803</v>
+        <v>-5.544989143975356</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.4071403654624</v>
+        <v>2.413281750147779</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8710963798074017</v>
+        <v>0.8576346460006611</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.154291659936111</v>
+        <v>5.146214619652066</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.628041499766604</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.397234613535188</v>
+        <v>-5.381881151821741</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.468791230038781</v>
+        <v>2.47493261472416</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.034204371961017</v>
+        <v>1.020742638154276</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.248564122943214</v>
+        <v>5.24048708265917</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.637088536457732</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.37659152273396</v>
+        <v>-5.361238061020513</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.486095503050401</v>
+        <v>2.492236887735779</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.034204371961017</v>
+        <v>1.020742638154276</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.257611159634342</v>
+        <v>5.249534119350298</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.637946001443853</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.439299439208519</v>
+        <v>-5.423945977495071</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.461869801446699</v>
+        <v>2.468011186132077</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9714964554864592</v>
+        <v>0.9580347216797186</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.22084387473573</v>
+        <v>5.212766834451685</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.600855418234206</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.391291315364826</v>
+        <v>-5.375937853651378</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.443982467774528</v>
+        <v>2.450123852459907</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9714964554864592</v>
+        <v>0.9580347216797186</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.183753291526082</v>
+        <v>5.175676251242037</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.604787671792156</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.241173260142928</v>
+        <v>-5.225819798429481</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.507961943421237</v>
+        <v>2.514103328106617</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.121614510708356</v>
+        <v>1.108152776901616</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.27775637821717</v>
+        <v>5.269679337933126</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.599686764399193</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.146615748769569</v>
+        <v>-5.131262287056122</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.540684040577618</v>
+        <v>2.546825425262997</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.121614510708356</v>
+        <v>1.108152776901616</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.272655470824207</v>
+        <v>5.264578430540163</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.595040673788288</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.028442370751641</v>
+        <v>-5.013088909038194</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.583307301173885</v>
+        <v>2.589448685859264</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.239787888726283</v>
+        <v>1.226326154919543</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.338913407024059</v>
+        <v>5.330836366740014</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.624129266651315</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.939595253892143</v>
+        <v>-4.924241792178696</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.647934740780711</v>
+        <v>2.654076125466089</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.328635005585781</v>
+        <v>1.31517327177904</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.421310270002784</v>
+        <v>5.41323322971874</v>
       </c>
     </row>
     <row r="2104">
@@ -49943,16 +49943,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.91254621619889</v>
+        <v>-4.897192754485443</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.652314578869189</v>
+        <v>2.658455963554568</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.355684043279035</v>
+        <v>1.342222309472294</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.431099915629913</v>
+        <v>5.423022875345869</v>
       </c>
     </row>
     <row r="2105">
@@ -49966,16 +49966,16 @@
         <v>4.617689489662492</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.91857949638566</v>
+        <v>-4.903226034672213</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.649901266794481</v>
+        <v>2.65604265147986</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.355684043279035</v>
+        <v>1.342222309472294</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.431099915629913</v>
+        <v>5.423022875345869</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.621327656804905</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.970431271958821</v>
+        <v>-4.955077810245374</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.632798723707629</v>
+        <v>2.638940108393008</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.303832267705873</v>
+        <v>1.290370533899133</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.403627017428429</v>
+        <v>5.395549977144385</v>
       </c>
     </row>
     <row r="2107">
@@ -50012,16 +50012,16 @@
         <v>4.584819403988742</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.997488718090648</v>
+        <v>-4.982135256377201</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.585467492438735</v>
+        <v>2.591608877124114</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.303832267705873</v>
+        <v>1.290370533899133</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.367118764612266</v>
+        <v>5.359041724328222</v>
       </c>
     </row>
     <row r="2108">
@@ -50035,16 +50035,16 @@
         <v>4.586227353735933</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.070770069944524</v>
+        <v>-5.055416608231076</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.557562901444376</v>
+        <v>2.563704286129755</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.289920845574662</v>
+        <v>1.276459111767921</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.360179861080731</v>
+        <v>5.352102820796686</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.786339171305457</v>
+        <v>3.824710234932239</v>
       </c>
       <c r="C2109" t="n">
         <v>4.604467567238743</v>
       </c>
       <c r="D2109" t="n">
-        <v>-4.990126659271492</v>
+        <v>-4.974773197558044</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.608060479216399</v>
+        <v>2.614201863901778</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.289920845574662</v>
+        <v>1.276459111767921</v>
       </c>
       <c r="G2109" t="n">
-        <v>5.37842007458354</v>
+        <v>5.370343034299496</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241007.xlsx
+++ b/tame_output/ON/bt/strategyON_20241007.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>148.8%</t>
+          <t>147.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>120.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.1%</t>
+          <t>423.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.1%</t>
+          <t>-637.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,32 +1145,32 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-114.8%</t>
+          <t>-107.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.2%</t>
+          <t>-278.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.3%</t>
+          <t>-128.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343075</v>
+        <v>3.785306190072577</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.615518808559632</v>
+        <v>-3.617123409902374</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.660863254189574</v>
+        <v>1.660221413652477</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.6414339571859208</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492854507887501</v>
+        <v>3.492287576238726</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389358</v>
+        <v>3.785306190072577</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.120500608793092</v>
+        <v>3.107427201927174</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.723819470429751</v>
+        <v>-3.617123409902374</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.630616396307444</v>
+        <v>1.660221413652477</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6423788432672118</v>
+        <v>0.6414339571859208</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.505927914753419</v>
+        <v>3.492287576238726</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.752237341573212</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.112505805576032</v>
+        <v>3.107427201927174</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.883370543193268</v>
+        <v>-3.618685052717233</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.558801163984977</v>
+        <v>1.659596756526533</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4901011764054604</v>
+        <v>0.6414339571859208</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.406566511419308</v>
+        <v>3.492287576238726</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.718174545201795</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.111029846703034</v>
+        <v>3.105951243054176</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.911271330302741</v>
+        <v>-3.646585839826706</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.54616489026819</v>
+        <v>1.646960482809746</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4555042522625256</v>
+        <v>0.606837033042986</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.38433239806055</v>
+        <v>3.470053462879967</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.687250428982208</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.107794290680233</v>
+        <v>3.102715687031374</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.033797433005635</v>
+        <v>-3.7691119425296</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.493918893164232</v>
+        <v>1.594714485705786</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3329781495596317</v>
+        <v>0.4843109303400921</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.307581180416012</v>
+        <v>3.39330224523543</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.621702731780758</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.174500250270737</v>
+        <v>3.169421646621878</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.264311929191224</v>
+        <v>-3.999626438715189</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.4684190542805</v>
+        <v>1.569214646822055</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.102463653374043</v>
+        <v>0.2537964341545034</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.235978442295163</v>
+        <v>3.32169950711458</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781467</v>
+        <v>3.643104738009488</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.314811969272584</v>
+        <v>3.309733365623725</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.613057014415667</v>
+        <v>-4.348371523939632</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.469232739192569</v>
+        <v>1.570028331734124</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.1450484802356056</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.311041388945671</v>
+        <v>3.396762453765088</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237099</v>
+        <v>3.670643654431918</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.383792238418224</v>
+        <v>3.378713634769364</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.767043432191808</v>
+        <v>-4.502357941715773</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.476618441227753</v>
+        <v>1.577414033769308</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.1450484802356056</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.380021658091311</v>
+        <v>3.465742722910728</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423392</v>
+        <v>3.622277666618211</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.369843440538344</v>
+        <v>3.364764836889485</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.971642867054817</v>
+        <v>-4.706957376578782</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.380829869402671</v>
+        <v>1.481625461944226</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.1450484802356056</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.366072860211432</v>
+        <v>3.451793925030849</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.658687383804576</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.381713929593758</v>
+        <v>3.376635325944899</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.224118021062541</v>
+        <v>-4.959432530586506</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.291710296854995</v>
+        <v>1.39250588939655</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.1450484802356056</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.377943349266846</v>
+        <v>3.463664414086263</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.67638318616798</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.382924464112702</v>
+        <v>3.377845860463843</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.517013777541953</v>
+        <v>-5.252328287065918</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.175762528782174</v>
+        <v>1.276558121323728</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.006284300544854848</v>
+        <v>0.1450484802356056</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.37915388378579</v>
+        <v>3.464874948605207</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.665864107446769</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.387046206340024</v>
+        <v>3.381967602691164</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.703677905676761</v>
+        <v>-5.438992415200726</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.105218619755572</v>
+        <v>1.206014212297127</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.03302327136941474</v>
+        <v>0.1183095094110457</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.367232243518375</v>
+        <v>3.452953308337792</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.654503803111024</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.382124059076213</v>
+        <v>3.377045455427354</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.849698592590723</v>
+        <v>-5.585013102114688</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.041888197726176</v>
+        <v>1.142683790267731</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.1092264176171887</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.35686024117825</v>
+        <v>3.442581305997667</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.670316957025151</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.544328115775257</v>
+        <v>3.539249512126398</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.941412601700309</v>
+        <v>-5.676727111224274</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.167406650781386</v>
+        <v>1.268202243322941</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.04210636316327171</v>
+        <v>0.1092264176171887</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.519064297877294</v>
+        <v>3.604785362696711</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071556</v>
+        <v>3.698894118266375</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.539174753739071</v>
+        <v>3.534096150090212</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.973064260760278</v>
+        <v>-5.708378770284243</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.149592625121213</v>
+        <v>1.250388217662767</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04727482040771191</v>
+        <v>0.1040579603727485</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.510809861494444</v>
+        <v>3.596530926313862</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868154</v>
+        <v>3.752398666062972</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.549404171307562</v>
+        <v>3.544325567658703</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.042130315333215</v>
+        <v>-5.77744482485718</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.132195620860529</v>
+        <v>1.232991213402084</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1096456979013219</v>
+        <v>0.04168708287913847</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.483616752566769</v>
+        <v>3.569337817386187</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332701</v>
+        <v>3.785987517527518</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.558329809763465</v>
+        <v>3.553251206114606</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.144106437581622</v>
+        <v>-5.879420947105587</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.100330810417069</v>
+        <v>1.201126402958624</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2116218201497295</v>
+        <v>-0.0602890393692691</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.431356717673627</v>
+        <v>3.517077782493045</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231818</v>
+        <v>3.719205168712484</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.55048269700764</v>
+        <v>3.545404093358781</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.034100154104401</v>
+        <v>-5.758558374751757</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.136486211052132</v>
+        <v>1.241624319144331</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1884172482324543</v>
+        <v>-0.03111830858008791</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.437432348068168</v>
+        <v>3.526733108210728</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818525</v>
+        <v>3.792635726548077</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.554732707729614</v>
+        <v>3.545404093358781</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.04662985921628</v>
+        <v>-5.749548796138429</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.135724339729355</v>
+        <v>1.245228150589663</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2022437476989773</v>
+        <v>-0.03111830858008791</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.433386459110229</v>
+        <v>3.526733108210728</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051791</v>
+        <v>3.784309213781343</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.56199359061215</v>
+        <v>3.552664976241317</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.745183133744442</v>
+        <v>-5.448102070666591</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.263563912800626</v>
+        <v>1.373067723660933</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.2703284168917494</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.621515377275867</v>
+        <v>3.714862026376367</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679629</v>
+        <v>3.819707742409181</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.562964768364861</v>
+        <v>3.553636153994028</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.769773377979626</v>
+        <v>-5.472692314901775</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.254698992859264</v>
+        <v>1.364202803719571</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.2703284168917494</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.622486555028577</v>
+        <v>3.715833204129078</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.828255984203715</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.563807672744617</v>
+        <v>3.554479058373783</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.718735001973106</v>
+        <v>-5.421653938895255</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.275957247641627</v>
+        <v>1.385461058501934</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.09920297777285991</v>
+        <v>0.2703284168917494</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.623329459408333</v>
+        <v>3.716676108508833</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969548</v>
+        <v>3.8388063186991</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.582845771618762</v>
+        <v>3.573517157247929</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.689886325149645</v>
+        <v>-5.392805262071795</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.306534817245157</v>
+        <v>1.416038628105464</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1280516545963202</v>
+        <v>0.2991770937152096</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.659676764376554</v>
+        <v>3.753023413477055</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700484</v>
+        <v>3.832824734430035</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.399029767742697</v>
+        <v>3.389701153371863</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.593251413131005</v>
+        <v>-5.296170350053155</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.161372778176547</v>
+        <v>1.270876589036854</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2246865666149601</v>
+        <v>0.3958120057338496</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.533841707711673</v>
+        <v>3.627188356812173</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077647</v>
+        <v>3.811760762807199</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.402531811816661</v>
+        <v>3.393203197445827</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.524213402182538</v>
+        <v>-5.227132339104687</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.192490026629899</v>
+        <v>1.301993837490206</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2937245775634282</v>
+        <v>0.4648500166823176</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.578766558354718</v>
+        <v>3.672113207455218</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833467</v>
+        <v>3.782100662563019</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.386958630892743</v>
+        <v>3.37763001652191</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.505426301813599</v>
+        <v>-5.208345238735748</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.184431685853557</v>
+        <v>1.293935496713864</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.4836371170512561</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.574465637652164</v>
+        <v>3.667812286752664</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077632</v>
+        <v>3.828102461807184</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.386146341329173</v>
+        <v>3.37681772695834</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.428327700271726</v>
+        <v>-5.131246637193875</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.214458836906735</v>
+        <v>1.323962647767042</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3125116779323667</v>
+        <v>0.4836371170512561</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.573653348088593</v>
+        <v>3.666999997189094</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147914</v>
+        <v>3.839378825877466</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.396015120454245</v>
+        <v>3.386686506083412</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.438712895161616</v>
+        <v>-5.141631832083765</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.220173538075852</v>
+        <v>1.329677348936159</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3021264830424774</v>
+        <v>0.4732519221613668</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.577291010279732</v>
+        <v>3.670637659380232</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373529</v>
+        <v>3.841487295464842</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.466852126230671</v>
+        <v>3.457523511859837</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.457301053883841</v>
+        <v>-5.16021999080599</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.283575280363387</v>
+        <v>1.393079091223694</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.283538324320252</v>
+        <v>0.4546637634391414</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.636975120822822</v>
+        <v>3.730321769923322</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496559</v>
+        <v>3.86219233722611</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.463721137048969</v>
+        <v>3.454392522678136</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.457599600579877</v>
+        <v>-5.160518537502026</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.280324872503271</v>
+        <v>1.389828683363578</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2832397776242161</v>
+        <v>0.4543652167431055</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.633665003623499</v>
+        <v>3.727011652723999</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108865</v>
+        <v>3.822715013838417</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.468252031988361</v>
+        <v>3.458923417617527</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.356776466889449</v>
+        <v>-5.059695403811598</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.325185020918834</v>
+        <v>1.434688831779141</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2957039931085699</v>
+        <v>0.4668294322274594</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.645674427853503</v>
+        <v>3.739021076954003</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121477</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.468381285466904</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.165995106137041</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.40162681869834</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4864853538609773</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.76027249778349</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390609</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.4482181312045</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.059031748287619</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.424249007575705</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.775188108296968</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912995</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.483185067816559</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.003701160385857</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.481348179348469</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.843353397650084</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539904</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.476871635717997</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.978338052546152</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.485179990385788</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6256436575622454</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.852257830255344</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481102</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.478752265902132</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.055693542674121</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.456118424518737</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.548288167434276</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.807725166362698</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438293</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.491603291780015</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.987644979982591</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.496188875473231</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6163367301258058</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.861405329855498</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013437</v>
+        <v>3.485340895838118</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.511805961953609</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.219245373152092</v>
+        <v>-4.846330594176997</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.423751388379025</v>
+        <v>1.520164009111525</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6163367301258058</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.881608000029093</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498973</v>
+        <v>3.773633099000463</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.495412198020491</v>
+        <v>3.459052671096071</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.269296918681311</v>
+        <v>-4.864403102468608</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.387337006234219</v>
+        <v>1.51293500579488</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6163367301258058</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.865214236095975</v>
+        <v>3.867169216213307</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800102</v>
+        <v>3.776934600301592</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.455664111613958</v>
+        <v>3.419304584689537</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.444403751257756</v>
+        <v>-5.039509935045054</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.277546186797108</v>
+        <v>1.403144186357768</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6163367301258058</v>
+        <v>0.680194241862061</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.825466149689441</v>
+        <v>3.827421129806774</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660855</v>
+        <v>3.852459046162345</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.462686730610898</v>
+        <v>3.426327203686477</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.248303597827233</v>
+        <v>-4.843409781614531</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.363008867166257</v>
+        <v>1.488606866726918</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8124368835563287</v>
+        <v>0.8762943952925839</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.950148860744696</v>
+        <v>3.952103840862028</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395092</v>
+        <v>3.837456370896582</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.561857730183802</v>
+        <v>3.525498203259382</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.095278205713949</v>
+        <v>-4.690384389501246</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.523390023584475</v>
+        <v>1.648988023145136</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9654622756696128</v>
+        <v>1.029319787405868</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.14113509558557</v>
+        <v>4.143090075702903</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791154</v>
+        <v>3.848164230292644</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.749323955092095</v>
+        <v>3.712964428167674</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.123585519587219</v>
+        <v>-4.718691703374517</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.69953332294346</v>
+        <v>1.82513132250412</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9654622756696128</v>
+        <v>1.029319787405868</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.328601320493862</v>
+        <v>4.330556300611195</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69911561562044</v>
+        <v>3.80600151312193</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.718726906446177</v>
+        <v>3.682367379521757</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.290178744700741</v>
+        <v>-4.885284928488039</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.602298984252134</v>
+        <v>1.727896983812794</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7988690505560905</v>
+        <v>0.8627265622923457</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.198048336779832</v>
+        <v>4.200003316897164</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285653</v>
+        <v>3.815068416787143</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.722403309107895</v>
+        <v>3.686043782183475</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.267142951339175</v>
+        <v>-4.862249135126473</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.615189704258478</v>
+        <v>1.740787703819138</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7988690505560905</v>
+        <v>0.8627265622923457</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.201724739441549</v>
+        <v>4.203679719558882</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399474</v>
+        <v>3.847467298900964</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.72002136423139</v>
+        <v>3.68366183730697</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.237896970883479</v>
+        <v>-4.833003154670776</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.624506151564252</v>
+        <v>1.750104151124912</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7988690505560905</v>
+        <v>0.8627265622923457</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.199342794565045</v>
+        <v>4.201297774682377</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256377</v>
+        <v>3.806290539757867</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.717314603389025</v>
+        <v>3.680955076464605</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.34482251876133</v>
+        <v>-4.939928702548627</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.579029171570746</v>
+        <v>1.704627171131407</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6919435026782391</v>
+        <v>0.7558010144144943</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.132480704995969</v>
+        <v>4.134435685113302</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701007</v>
+        <v>3.796828498202498</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.71874340553226</v>
+        <v>3.682383878607839</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.489841077268578</v>
+        <v>-5.084947261055876</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.522450550311081</v>
+        <v>1.648048549871741</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5469249441709906</v>
+        <v>0.6107824559072458</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.046898372034854</v>
+        <v>4.048853352152187</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687019</v>
+        <v>3.818738327188509</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.818674644790013</v>
+        <v>3.782315117865592</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.608182843053296</v>
+        <v>-5.203289026840594</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.575045083254947</v>
+        <v>1.700643082815607</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5576109827338807</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.153241234430341</v>
+        <v>4.155196214547674</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790811</v>
+        <v>3.821764949292302</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.816460341915952</v>
+        <v>3.780100814991531</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.659593265374004</v>
+        <v>-5.254699449161301</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.552266611452603</v>
+        <v>1.677864611013263</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5576109827338807</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.15102693155628</v>
+        <v>4.152981911673613</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943734</v>
+        <v>3.81164384693883</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.816363469990241</v>
+        <v>3.78000394306582</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.739012716581755</v>
+        <v>-5.334118900369053</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.520401959043792</v>
+        <v>1.645999958604452</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5576109827338807</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.15093005963057</v>
+        <v>4.152885039747902</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298408</v>
+        <v>3.97377273195735</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.816357363548284</v>
+        <v>3.779997836623863</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.834475714498973</v>
+        <v>-5.416691361494864</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.482210653434947</v>
+        <v>1.61296486771217</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5576109827338807</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.150923953188612</v>
+        <v>4.152878933305945</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218011</v>
+        <v>3.97377273195735</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.814453760110895</v>
+        <v>3.779997836623863</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.770099803648258</v>
+        <v>-5.416691361494864</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.506057414337844</v>
+        <v>1.61296486771217</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6219868935845958</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.187645896261652</v>
+        <v>4.152878933305945</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353547</v>
+        <v>3.97377273195735</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.820187577858621</v>
+        <v>3.779997836623863</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.825468965780452</v>
+        <v>-5.416691361494864</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.489643567232693</v>
+        <v>1.61296486771217</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6219868935845958</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.193379714009379</v>
+        <v>4.152878933305945</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011329</v>
+        <v>3.97377273195735</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.819725941201554</v>
+        <v>3.779997836623863</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.843687432778061</v>
+        <v>-5.416691361494864</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.481894543776582</v>
+        <v>1.61296486771217</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5968804563287536</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.177854214998806</v>
+        <v>4.152878933305945</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113699</v>
+        <v>3.97377273195735</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.839600334051872</v>
+        <v>3.779997836623863</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.80500399743413</v>
+        <v>-5.416691361494864</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.517242310764473</v>
+        <v>1.61296486771217</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5968804563287536</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.197728607849124</v>
+        <v>4.152878933305945</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.912846965851127</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.8233010345766</v>
+        <v>3.779997836623863</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.698969002228821</v>
+        <v>-5.414000508294682</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.543357009371324</v>
+        <v>1.614041208992243</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5968804563287536</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.181429308373852</v>
+        <v>4.152878933305945</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307675</v>
+        <v>3.913065215142359</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.825731984040646</v>
+        <v>3.782428786087909</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.515757339095726</v>
+        <v>-5.230788845161586</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.619072624088608</v>
+        <v>1.689756823709527</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5968804563287536</v>
+        <v>0.6214684944701359</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.183860257837899</v>
+        <v>4.155309882769991</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863556</v>
+        <v>3.89520667969824</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.808676390120023</v>
+        <v>3.765373192167286</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.444035892081875</v>
+        <v>-5.159067398147736</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.630705608973526</v>
+        <v>1.701389808594445</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6686019033426043</v>
+        <v>0.6931899414839865</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.209837532125586</v>
+        <v>4.181287157057678</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394118</v>
+        <v>3.842149827228802</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.755592136041195</v>
+        <v>3.712288938088458</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.421662866474168</v>
+        <v>-5.136694372540029</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.58657056513778</v>
+        <v>1.657254764758699</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6798576544555058</v>
+        <v>0.7044456925968881</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.163506728714498</v>
+        <v>4.134956353646591</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456736</v>
+        <v>3.83396756829142</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.94079034092655</v>
+        <v>3.897487142973813</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.454679162384913</v>
+        <v>-5.169710668450774</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.758562251658837</v>
+        <v>1.829246451279756</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6104202777887542</v>
+        <v>0.6350083159301365</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.307042507599803</v>
+        <v>4.278492132531896</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883687</v>
+        <v>3.832122658718371</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.932711566754799</v>
+        <v>3.889408368802063</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.443151526735305</v>
+        <v>-5.158183032801166</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.75509453174693</v>
+        <v>1.825778731367849</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6694209359901167</v>
+        <v>0.694008974131499</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.334364128348869</v>
+        <v>4.305813753280963</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236308</v>
+        <v>3.939589964586375</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.936379679276587</v>
+        <v>3.893076481323851</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.540493028077673</v>
+        <v>-5.255731774006746</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.719826043731771</v>
+        <v>1.790427347407406</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6250007538246283</v>
+        <v>0.6489463668615292</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.311380131571365</v>
+        <v>4.282444301440769</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427695</v>
+        <v>3.939589964586375</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.937630761469426</v>
+        <v>3.893076481323851</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.62634905741764</v>
+        <v>-5.255731774006746</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.686734714188622</v>
+        <v>1.790427347407406</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5826246845984933</v>
+        <v>0.6489463668615292</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.287205572228522</v>
+        <v>4.282444301440769</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610386</v>
+        <v>3.822819149114461</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.920049963289927</v>
+        <v>3.893076481323851</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.635185854833759</v>
+        <v>-5.259481139925343</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.665619197042676</v>
+        <v>1.788927601039966</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5751825119571425</v>
+        <v>0.6489463668615292</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.265159470464213</v>
+        <v>4.282444301440769</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667464</v>
+        <v>3.84652806117154</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.930214474334977</v>
+        <v>3.903240992368901</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.726568417399218</v>
+        <v>-5.350863702490802</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.639230683061542</v>
+        <v>1.762539087058832</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5386176272377978</v>
+        <v>0.6123814821421845</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.253385050677656</v>
+        <v>4.270669881654212</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889202</v>
+        <v>3.834962531913027</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.032342732159245</v>
+        <v>4.005369250193168</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.714861699412212</v>
+        <v>-5.352997470856717</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.746041628080613</v>
+        <v>1.863813837536734</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5503243452248042</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.362537339294128</v>
+        <v>4.37151787845893</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409577</v>
+        <v>3.812850798281435</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.03537507089065</v>
+        <v>4.005369250193168</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.785773773154489</v>
+        <v>-5.351921148956471</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.720709137315107</v>
+        <v>1.864244366296833</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5503243452248042</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.365569678025532</v>
+        <v>4.37151787845893</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452576</v>
+        <v>3.803269876324434</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.036193896622915</v>
+        <v>4.005369250193168</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.796089871320841</v>
+        <v>-5.351921148956471</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.717401523780831</v>
+        <v>1.864244366296833</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5503243452248042</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.366388503757797</v>
+        <v>4.37151787845893</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762297</v>
+        <v>3.919498914949401</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.035372563535004</v>
+        <v>4.005369250193168</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.795995903303468</v>
+        <v>-5.351921148956471</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.71661777789987</v>
+        <v>1.864244366296833</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.365789087478277</v>
+        <v>4.37151787845893</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.800870306884089</v>
+        <v>3.919498914949401</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.029604549479358</v>
+        <v>4.005369250193168</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.939597067326853</v>
+        <v>-5.351921148956471</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.653409298234869</v>
+        <v>1.864244366296833</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.360021073422631</v>
+        <v>4.37151787845893</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.671015692129653</v>
+        <v>3.792052432567817</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.029604549479358</v>
+        <v>4.005369250193168</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.938648644208815</v>
+        <v>-5.350972725838433</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.653788667482085</v>
+        <v>1.864623735544048</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.360021073422631</v>
+        <v>4.37151787845893</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.904173816052356</v>
+        <v>4.025210556490521</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.04233215746045</v>
+        <v>4.01809685817426</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.038918462167835</v>
+        <v>-5.451242543797454</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.626408348279568</v>
+        <v>1.837243416341531</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.372748681403723</v>
+        <v>4.384245486440022</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.7401796078135</v>
+        <v>3.861216348251665</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.044278155884838</v>
+        <v>4.020042856598648</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.032926215379024</v>
+        <v>-5.445250297008642</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.630751245419481</v>
+        <v>1.841586313481444</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.374694679828111</v>
+        <v>4.38619148486441</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.765050796537949</v>
+        <v>3.886087536976113</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.037932291902607</v>
+        <v>4.013696992616417</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.944368254248256</v>
+        <v>-5.356692335877875</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.659828565889557</v>
+        <v>1.87066363395152</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.36834881584588</v>
+        <v>4.379845620882179</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.758409170771821</v>
+        <v>3.879445911209985</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.037240969341602</v>
+        <v>4.013005670055413</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.926609176745182</v>
+        <v>-5.338933258374801</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.666240874329782</v>
+        <v>1.877075942391745</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5506942065721222</v>
+        <v>0.6102477137762693</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.367657493284876</v>
+        <v>4.379154298321175</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.801340597109727</v>
+        <v>3.922377337547891</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.050023155250189</v>
+        <v>4.025787855963999</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.826979025696114</v>
+        <v>-5.239303107325733</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.718875120657996</v>
+        <v>1.929710188719959</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6503243576211897</v>
+        <v>0.7098778648253368</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.440217769822903</v>
+        <v>4.451714574859202</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.798465546844001</v>
+        <v>3.919502287282165</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.239177420748915</v>
+        <v>4.214942121462726</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.876378534385125</v>
+        <v>-5.288702616014744</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.888269582681118</v>
+        <v>2.099104650743081</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6605831910529344</v>
+        <v>0.7201366982570815</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.635527335380677</v>
+        <v>4.647024140416975</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.772186508351865</v>
+        <v>3.893223248790029</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.226366093851778</v>
+        <v>4.202130794565588</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.669694060742749</v>
+        <v>-5.082018142372368</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.958132045240931</v>
+        <v>2.168967113302894</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.86726766469531</v>
+        <v>0.9268211718994571</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.746726692668964</v>
+        <v>4.758223497705263</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763392838551275</v>
+        <v>3.884429578989439</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.228367607505882</v>
+        <v>4.204132308219693</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.703850955740275</v>
+        <v>-5.116175037369894</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.946470800896025</v>
+        <v>2.157305868957988</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7836838951544975</v>
+        <v>0.8432374023586446</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.698577944598581</v>
+        <v>4.71007474963488</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.805590565041117</v>
+        <v>3.926627305479281</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.58186472149555</v>
+        <v>4.55762942220936</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.611261476678819</v>
+        <v>-5.023585558308437</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.337003706510275</v>
+        <v>2.547838774572238</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7836838951544975</v>
+        <v>0.8432374023586446</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.052075058588248</v>
+        <v>5.063571863624547</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.832164354497408</v>
+        <v>3.953201094935572</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.586427833062654</v>
+        <v>4.562192533776464</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.684422080451964</v>
+        <v>-5.096746162081582</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.312302576568121</v>
+        <v>2.523137644630084</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7556626951202545</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.039825450134807</v>
+        <v>5.051322255171105</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.858310890492302</v>
+        <v>3.908785935266827</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.636257774386181</v>
+        <v>4.612022475099992</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.632205770655622</v>
+        <v>-5.050099907305197</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.383019041810186</v>
+        <v>2.591626087864166</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7556626951202545</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.089655391458335</v>
+        <v>5.101152196494633</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.844935596436483</v>
+        <v>3.908785935266827</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.645071744596192</v>
+        <v>4.612022475099992</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.579698443145127</v>
+        <v>-5.050099907305197</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.412835943024394</v>
+        <v>2.591626087864166</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8081700226307494</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.129973758174643</v>
+        <v>5.101152196494633</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.848376866039493</v>
+        <v>3.908785935266827</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.640709328635389</v>
+        <v>4.612022475099992</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.594453767345268</v>
+        <v>-5.050099907305197</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.402571397383535</v>
+        <v>2.591626087864166</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8081700226307494</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.12561134221384</v>
+        <v>5.101152196494633</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.868153115524487</v>
+        <v>3.908785935266827</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.631633832051669</v>
+        <v>4.612022475099992</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.544989143975356</v>
+        <v>-5.050099907305197</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.413281750147779</v>
+        <v>2.591626087864166</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8576346460006611</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.146214619652066</v>
+        <v>5.101152196494633</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.849040239867961</v>
+        <v>3.908785935266827</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.628041499766604</v>
+        <v>4.612022475099992</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.381881151821741</v>
+        <v>-5.050099907305197</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.47493261472416</v>
+        <v>2.591626087864166</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.020742638154276</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.24048708265917</v>
+        <v>5.101152196494633</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.870204928232976</v>
+        <v>3.994720839830584</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.637088536457732</v>
+        <v>4.612022475099992</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.361238061020513</v>
+        <v>-5.052850023294524</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.492236887735779</v>
+        <v>2.590526041468435</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.020742638154276</v>
+        <v>0.8152162023244016</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.249534119350298</v>
+        <v>5.101152196494633</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.85553443717968</v>
+        <v>3.980050348777287</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.637946001443853</v>
+        <v>4.612879940086113</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.423945977495071</v>
+        <v>-5.115557939769082</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.468011186132077</v>
+        <v>2.566300339864733</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9580347216797186</v>
+        <v>0.7525082858498439</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.212766834451685</v>
+        <v>5.06438491159602</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.884687848967727</v>
+        <v>4.009203760565335</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.600855418234206</v>
+        <v>4.575789356876466</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.375937853651378</v>
+        <v>-5.067549815925389</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.450123852459907</v>
+        <v>2.548413006192563</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9580347216797186</v>
+        <v>0.7525082858498439</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.175676251242037</v>
+        <v>5.027294328386372</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.895362357018618</v>
+        <v>4.019878268616226</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.604787671792156</v>
+        <v>4.579721610434415</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.225819798429481</v>
+        <v>-4.917431760703492</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.514103328106617</v>
+        <v>2.612392481839271</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.108152776901616</v>
+        <v>0.9026263410717409</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.269679337933126</v>
+        <v>5.12129741507746</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.891610981075141</v>
+        <v>4.016126892672749</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.599686764399193</v>
+        <v>4.574620703041452</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.131262287056122</v>
+        <v>-4.822874249330132</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.546825425262997</v>
+        <v>2.645114578995652</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.108152776901616</v>
+        <v>0.9026263410717409</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.264578430540163</v>
+        <v>5.116196507684497</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.872432493435451</v>
+        <v>3.914573818819656</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.595040673788288</v>
+        <v>4.569974612430547</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.013088909038194</v>
+        <v>-4.714014736096746</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.589448685859264</v>
+        <v>2.684012293678101</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.226326154919543</v>
+        <v>1.011485854305127</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.330836366740014</v>
+        <v>5.176866125013624</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.85957172391774</v>
+        <v>3.914573818819656</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.624129266651315</v>
+        <v>4.569974612430547</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.924241792178696</v>
+        <v>-4.714014736096746</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.654076125466089</v>
+        <v>2.684012293678101</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.31517327177904</v>
+        <v>1.011485854305127</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.41323322971874</v>
+        <v>5.176866125013624</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.828006274013646</v>
+        <v>3.914573818819656</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.617689489662492</v>
+        <v>4.569974612430547</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.897192754485443</v>
+        <v>-4.714014736096746</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.658455963554568</v>
+        <v>2.684012293678101</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.342222309472294</v>
+        <v>1.011485854305127</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.423022875345869</v>
+        <v>5.176866125013624</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.823987445263776</v>
+        <v>3.95400890080217</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.617689489662492</v>
+        <v>4.569974612430547</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.903226034672213</v>
+        <v>-4.720048016283516</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.65604265147986</v>
+        <v>2.681598981603393</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.342222309472294</v>
+        <v>1.011485854305127</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.423022875345869</v>
+        <v>5.176866125013624</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>3.81565720317085</v>
+        <v>4.040997056470527</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.621327656804905</v>
+        <v>4.57361277957296</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.955077810245374</v>
+        <v>-4.766897045101583</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.638940108393008</v>
+        <v>2.66649753721858</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.290370533899133</v>
+        <v>0.9646368254870601</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.395549977144385</v>
+        <v>5.152394874865196</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.830586986431413</v>
+        <v>3.966927267586609</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.584819403988742</v>
+        <v>4.57361277957296</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.982135256377201</v>
+        <v>-4.76450818731155</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.591608877124114</v>
+        <v>2.667453080334592</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.290370533899133</v>
+        <v>0.9646368254870601</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.359041724328222</v>
+        <v>5.152394874865196</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.83085645723246</v>
+        <v>3.967196738387655</v>
       </c>
       <c r="C2108" t="n">
-        <v>4.586227353735933</v>
+        <v>4.575020729320151</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.055416608231076</v>
+        <v>-4.837789539165425</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.563704286129755</v>
+        <v>2.639548489340234</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.276459111767921</v>
+        <v>0.9507254033558485</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.352102820796686</v>
+        <v>5.145455971333661</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.824710234932239</v>
+        <v>3.996092160492793</v>
       </c>
       <c r="C2109" t="n">
-        <v>4.604467567238743</v>
+        <v>4.593260942822961</v>
       </c>
       <c r="D2109" t="n">
-        <v>-4.974773197558044</v>
+        <v>-4.757146128492393</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.614201863901778</v>
+        <v>2.690046067112256</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.276459111767921</v>
+        <v>0.9507254033558485</v>
       </c>
       <c r="G2109" t="n">
-        <v>5.370343034299496</v>
+        <v>5.16369618483647</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241007.xlsx
+++ b/tame_output/ON/bt/strategyON_20241007.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>101.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>147.7%</t>
+          <t>147.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>106.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.5%</t>
+          <t>423.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-637.3%</t>
+          <t>-674.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,52 +1145,52 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.2%</t>
+          <t>-122.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-278.5%</t>
+          <t>-202.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-128.9%</t>
+          <t>-112.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.166429528281172</v>
+        <v>-4.160862811117614</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6932582156675111</v>
+        <v>0.6954849025329342</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.122056396642603</v>
+        <v>-4.116489679479045</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7108703357583748</v>
+        <v>0.7130970226237978</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.087325075324102</v>
+        <v>-4.081758358160545</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7191566584243654</v>
+        <v>0.7213833452897886</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.039669344763047</v>
+        <v>-4.034102627599489</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7446007076765924</v>
+        <v>0.7468273945420156</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.939151186264292</v>
+        <v>-3.933584469100734</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.789700344450819</v>
+        <v>0.7919270313162423</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.923245856831939</v>
+        <v>-3.917679139668381</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7828171486996323</v>
+        <v>0.7850438355650555</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.878407455223541</v>
+        <v>-3.872840738059983</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8048502119536201</v>
+        <v>0.8070768988190433</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.897905911465549</v>
+        <v>-3.892339194301992</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8012117690878948</v>
+        <v>0.8034384559533181</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.853703074379649</v>
+        <v>-3.848136357216091</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8247725064500921</v>
+        <v>0.8269991933155154</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.861262740216696</v>
+        <v>-3.855696023053138</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8201586405845209</v>
+        <v>0.8223853274499442</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.702971322677424</v>
+        <v>-3.697404605513866</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9347229727832695</v>
+        <v>0.9369496596486926</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.495329319042948</v>
+        <v>-3.48976260187939</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.016220478831313</v>
+        <v>1.018447165696736</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.444297226320419</v>
+        <v>-3.438730509156862</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.031581544158594</v>
+        <v>1.033808231024018</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.379073045193214</v>
+        <v>-3.373506328029656</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.074858620702182</v>
+        <v>1.077085307567605</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.34164602512208</v>
+        <v>-3.336079307958522</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.085790401029916</v>
+        <v>1.088017087895339</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.340288040148534</v>
+        <v>-3.334721322984977</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.087590387350574</v>
+        <v>1.089817074215997</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.311874777048651</v>
+        <v>-3.306308059885093</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.259513463611738</v>
+        <v>1.261740150477161</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47367,10 +47367,10 @@
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.237092516023638</v>
+        <v>-3.23152579886008</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.409539277239561</v>
+        <v>1.411765964104984</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.21100843175983</v>
+        <v>-3.205441714596272</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.411680886958943</v>
+        <v>1.413907573824366</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47413,10 +47413,10 @@
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.12313051865071</v>
+        <v>-3.117563801487152</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.44502524778637</v>
+        <v>1.447251934651793</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.114238057257427</v>
+        <v>-3.108671340093869</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.466136638070475</v>
+        <v>1.468363324935898</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47459,10 +47459,10 @@
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.282714174227304</v>
+        <v>-3.277147457063747</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.390601238687108</v>
+        <v>1.392827925552531</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47482,10 +47482,10 @@
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.836457981597865</v>
+        <v>-2.830891264434307</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.550373412926745</v>
+        <v>1.552600099792169</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.813736877914712</v>
+        <v>-2.808170160751154</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.550125876896911</v>
+        <v>1.552352563762334</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.942938691208755</v>
+        <v>-2.937371974045197</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.657351277430463</v>
+        <v>1.659577964295886</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.96881308968278</v>
+        <v>-2.963246372519222</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.684079340534499</v>
+        <v>1.686306027399923</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.961758399467607</v>
+        <v>-2.956191682304049</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.683576572610114</v>
+        <v>1.685803259475537</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.934807175141119</v>
+        <v>-2.929240457977561</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.704363215985451</v>
+        <v>1.706589902850874</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.956351402971906</v>
+        <v>-2.950784685808348</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.879848656998096</v>
+        <v>1.882075343863519</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.978759520776778</v>
+        <v>-2.97319280361322</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.86300210477914</v>
+        <v>1.865228791644563</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.006983756354378</v>
+        <v>-3.00141703919082</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.853766410097737</v>
+        <v>1.85599309696316</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.016424682242908</v>
+        <v>-3.01085796507935</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.906243757464172</v>
+        <v>1.908470444329595</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.222663620031342</v>
+        <v>-3.217096902867784</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.8266392768941</v>
+        <v>1.828865963759523</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9241185524652205</v>
@@ -47735,10 +47735,10 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.298993597632248</v>
+        <v>-3.29342688046869</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.794219098747513</v>
+        <v>1.796445785612936</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9241185524652205</v>
@@ -47758,10 +47758,10 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.453950383032377</v>
+        <v>-3.448383665868819</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.727056614190323</v>
+        <v>1.729283301055746</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7691617670650912</v>
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.785306190072577</v>
+        <v>3.712897612343075</v>
       </c>
       <c r="C2010" t="n">
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.617123409902374</v>
+        <v>-3.609952091396074</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.660221413652477</v>
+        <v>1.663089941054997</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6414339571859208</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.492287576238726</v>
+        <v>3.492854507887501</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.785306190072577</v>
+        <v>3.754596135389358</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.107427201927174</v>
+        <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.617123409902374</v>
+        <v>-3.718252753266194</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.660221413652477</v>
+        <v>1.632843083172868</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6414339571859208</v>
+        <v>0.6423788432672118</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.492287576238726</v>
+        <v>3.505927914753419</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.752237341573212</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.107427201927174</v>
+        <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.618685052717233</v>
+        <v>-3.877803826029711</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.659596756526533</v>
+        <v>1.561027850850401</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6414339571859208</v>
+        <v>0.4901011764054604</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.492287576238726</v>
+        <v>3.406566511419308</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.718174545201795</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.105951243054176</v>
+        <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.646585839826706</v>
+        <v>-3.905704613139183</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.646960482809746</v>
+        <v>1.548391577133613</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.606837033042986</v>
+        <v>0.4555042522625256</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.470053462879967</v>
+        <v>3.38433239806055</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.687250428982208</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.102715687031374</v>
+        <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.7691119425296</v>
+        <v>-4.028230715842078</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.594714485705786</v>
+        <v>1.496145580029655</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4843109303400921</v>
+        <v>0.3329781495596317</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.39330224523543</v>
+        <v>3.307581180416012</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.621702731780758</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.169421646621878</v>
+        <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.999626438715189</v>
+        <v>-4.258745212027667</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.569214646822055</v>
+        <v>1.470645741145923</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2537964341545034</v>
+        <v>0.102463653374043</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.32169950711458</v>
+        <v>3.235978442295163</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.643104738009488</v>
+        <v>3.64075008781467</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.309733365623725</v>
+        <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.348371523939632</v>
+        <v>-4.60749029725211</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.570028331734124</v>
+        <v>1.471459426057992</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1450484802356056</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.396762453765088</v>
+        <v>3.311041388945671</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.670643654431918</v>
+        <v>3.668289004237099</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.378713634769364</v>
+        <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.502357941715773</v>
+        <v>-4.761476715028251</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.577414033769308</v>
+        <v>1.478845128093176</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1450484802356056</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.465742722910728</v>
+        <v>3.380021658091311</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.622277666618211</v>
+        <v>3.619923016423392</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.364764836889485</v>
+        <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.706957376578782</v>
+        <v>-4.96607614989126</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.481625461944226</v>
+        <v>1.383056556268093</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1450484802356056</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.451793925030849</v>
+        <v>3.366072860211432</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.658687383804576</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.376635325944899</v>
+        <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.959432530586506</v>
+        <v>-5.218551303898984</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.39250588939655</v>
+        <v>1.293936983720418</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1450484802356056</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.463664414086263</v>
+        <v>3.377943349266846</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67638318616798</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.377845860463843</v>
+        <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.252328287065918</v>
+        <v>-5.511447060378396</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.276558121323728</v>
+        <v>1.177989215647596</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1450484802356056</v>
+        <v>-0.006284300544854848</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.464874948605207</v>
+        <v>3.37915388378579</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.665864107446769</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.381967602691164</v>
+        <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.438992415200726</v>
+        <v>-5.698111188513204</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.206014212297127</v>
+        <v>1.107445306620995</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1183095094110457</v>
+        <v>-0.03302327136941474</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.452953308337792</v>
+        <v>3.367232243518375</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.654503803111024</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.377045455427354</v>
+        <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.585013102114688</v>
+        <v>-5.844131875427166</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.142683790267731</v>
+        <v>1.044114884591599</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1092264176171887</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.442581305997667</v>
+        <v>3.35686024117825</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.670316957025151</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.539249512126398</v>
+        <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.676727111224274</v>
+        <v>-5.935845884536752</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.268202243322941</v>
+        <v>1.169633337646809</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1092264176171887</v>
+        <v>-0.04210636316327171</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.604785362696711</v>
+        <v>3.519064297877294</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.698894118266375</v>
+        <v>3.696539468071556</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.534096150090212</v>
+        <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.708378770284243</v>
+        <v>-5.967497543596721</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.250388217662767</v>
+        <v>1.151819311986635</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1040579603727485</v>
+        <v>-0.04727482040771191</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.596530926313862</v>
+        <v>3.510809861494444</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.752398666062972</v>
+        <v>3.750044015868154</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.544325567658703</v>
+        <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.77744482485718</v>
+        <v>-6.036563598169658</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.232991213402084</v>
+        <v>1.134422307725952</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.04168708287913847</v>
+        <v>-0.1096456979013219</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.569337817386187</v>
+        <v>3.483616752566769</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.785987517527518</v>
+        <v>3.783632867332701</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.553251206114606</v>
+        <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.879420947105587</v>
+        <v>-6.138539720418065</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.201126402958624</v>
+        <v>1.102557497282491</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0602890393692691</v>
+        <v>-0.2116218201497295</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.517077782493045</v>
+        <v>3.431356717673627</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.719205168712484</v>
+        <v>3.798296784231818</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.545404093358781</v>
+        <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.758558374751757</v>
+        <v>-6.028533436940844</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.241624319144331</v>
+        <v>1.138712897917555</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.03111830858008791</v>
+        <v>-0.1884172482324543</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.526733108210728</v>
+        <v>3.437432348068168</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.792635726548077</v>
+        <v>3.785563924818525</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.545404093358781</v>
+        <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.749548796138429</v>
+        <v>-6.041063142052723</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.245228150589663</v>
+        <v>1.137951026594778</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.03111830858008791</v>
+        <v>-0.2022437476989773</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.526733108210728</v>
+        <v>3.433386459110229</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.784309213781343</v>
+        <v>3.777237412051791</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.552664976241317</v>
+        <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.448102070666591</v>
+        <v>-5.739616416580885</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.373067723660933</v>
+        <v>1.265790599666049</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2703284168917494</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.714862026376367</v>
+        <v>3.621515377275867</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.819707742409181</v>
+        <v>3.812635940679629</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.553636153994028</v>
+        <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.472692314901775</v>
+        <v>-5.764206660816069</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.364202803719571</v>
+        <v>1.256925679724686</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2703284168917494</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.715833204129078</v>
+        <v>3.622486555028577</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.828255984203715</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.554479058373783</v>
+        <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.421653938895255</v>
+        <v>-5.713168284809549</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.385461058501934</v>
+        <v>1.27818393450705</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2703284168917494</v>
+        <v>0.09920297777285991</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.716676108508833</v>
+        <v>3.623329459408333</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.8388063186991</v>
+        <v>3.831734516969548</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.573517157247929</v>
+        <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.392805262071795</v>
+        <v>-5.684319607986088</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.416038628105464</v>
+        <v>1.30876150411058</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2991770937152096</v>
+        <v>0.1280516545963202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.753023413477055</v>
+        <v>3.659676764376554</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.832824734430035</v>
+        <v>3.825752932700484</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.389701153371863</v>
+        <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.296170350053155</v>
+        <v>-5.587684695967448</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.270876589036854</v>
+        <v>1.16359946504197</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3958120057338496</v>
+        <v>0.2246865666149601</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.627188356812173</v>
+        <v>3.533841707711673</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.811760762807199</v>
+        <v>3.804688961077647</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.393203197445827</v>
+        <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.227132339104687</v>
+        <v>-5.518646685018981</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.301993837490206</v>
+        <v>1.194716713495321</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4648500166823176</v>
+        <v>0.2937245775634282</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.672113207455218</v>
+        <v>3.578766558354718</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.782100662563019</v>
+        <v>3.775028860833467</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.37763001652191</v>
+        <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.208345238735748</v>
+        <v>-5.499859584650042</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.293935496713864</v>
+        <v>1.186658372718979</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4836371170512561</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.667812286752664</v>
+        <v>3.574465637652164</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.828102461807184</v>
+        <v>3.821030660077632</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.37681772695834</v>
+        <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.131246637193875</v>
+        <v>-5.422760983108169</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.323962647767042</v>
+        <v>1.216685523772158</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4836371170512561</v>
+        <v>0.3125116779323667</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.666999997189094</v>
+        <v>3.573653348088593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.839378825877466</v>
+        <v>3.832307024147914</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.386686506083412</v>
+        <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.141631832083765</v>
+        <v>-5.433146177998059</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.329677348936159</v>
+        <v>1.222400224941275</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4732519221613668</v>
+        <v>0.3021264830424774</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.670637659380232</v>
+        <v>3.577291010279732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.841487295464842</v>
+        <v>3.83441549373529</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.457523511859837</v>
+        <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.16021999080599</v>
+        <v>-5.451734336720284</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.393079091223694</v>
+        <v>1.28580196722881</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4546637634391414</v>
+        <v>0.283538324320252</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.730321769923322</v>
+        <v>3.636975120822822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.86219233722611</v>
+        <v>3.855120535496559</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.454392522678136</v>
+        <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.160518537502026</v>
+        <v>-5.45203288341632</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.389828683363578</v>
+        <v>1.282551559368694</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4543652167431055</v>
+        <v>0.2832397776242161</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.727011652723999</v>
+        <v>3.633665003623499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.822715013838417</v>
+        <v>3.815643212108865</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.458923417617527</v>
+        <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.059695403811598</v>
+        <v>-5.351209749725892</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.434688831779141</v>
+        <v>1.327411707784257</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4668294322274594</v>
+        <v>0.2957039931085699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.739021076954003</v>
+        <v>3.645674427853503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.485340895838118</v>
+        <v>3.807356168121477</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.459052671096071</v>
+        <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.846330594176997</v>
+        <v>-5.160428388973484</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.520164009111525</v>
+        <v>1.403853505563763</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.680194241862061</v>
+        <v>0.4864853538609773</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.867169216213307</v>
+        <v>3.76027249778349</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.485340895838118</v>
+        <v>3.77523303390609</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.459052671096071</v>
+        <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.846330594176997</v>
+        <v>-5.053465031124063</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.520164009111525</v>
+        <v>1.426475694441128</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.680194241862061</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.867169216213307</v>
+        <v>3.775188108296968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.485340895838118</v>
+        <v>3.785761685912995</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.459052671096071</v>
+        <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.846330594176997</v>
+        <v>-4.9981344432223</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.520164009111525</v>
+        <v>1.483574866213891</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.680194241862061</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.867169216213307</v>
+        <v>3.843353397650084</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.485340895838118</v>
+        <v>3.743767956539904</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.459052671096071</v>
+        <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.846330594176997</v>
+        <v>-4.986080316309337</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.520164009111525</v>
+        <v>1.482083084880514</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.680194241862061</v>
+        <v>0.6123346766355037</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.867169216213307</v>
+        <v>3.844272441699299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.485340895838118</v>
+        <v>3.72501084481102</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.459052671096071</v>
+        <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.846330594176997</v>
+        <v>-5.063435806437306</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.520164009111525</v>
+        <v>1.453021519013463</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.680194241862061</v>
+        <v>0.5349791865075343</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.867169216213307</v>
+        <v>3.799739777806653</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.485340895838118</v>
+        <v>3.61232244438293</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.459052671096071</v>
+        <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.846330594176997</v>
+        <v>-4.995387243745776</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.520164009111525</v>
+        <v>1.493091969967957</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.680194241862061</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.867169216213307</v>
+        <v>3.853419941299454</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.485340895838118</v>
+        <v>3.645256780013437</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.459052671096071</v>
+        <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.846330594176997</v>
+        <v>-5.226987636915277</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.520164009111525</v>
+        <v>1.420654482873751</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.680194241862061</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.867169216213307</v>
+        <v>3.873622611473048</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.773633099000463</v>
+        <v>3.666747201498973</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.459052671096071</v>
+        <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.864403102468608</v>
+        <v>-5.277039182444497</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.51293500579488</v>
+        <v>1.384240100728945</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.680194241862061</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.867169216213307</v>
+        <v>3.85722884753993</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.776934600301592</v>
+        <v>3.670048702800102</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.419304584689537</v>
+        <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.039509935045054</v>
+        <v>-5.452146015020942</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.403144186357768</v>
+        <v>1.274449281291834</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.680194241862061</v>
+        <v>0.6030277491990641</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.827421129806774</v>
+        <v>3.817480761133397</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.852459046162345</v>
+        <v>3.745573148660855</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.426327203686477</v>
+        <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.843409781614531</v>
+        <v>-5.256045861590419</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.488606866726918</v>
+        <v>1.359911961660983</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8762943952925839</v>
+        <v>0.799127902629587</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.952103840862028</v>
+        <v>3.94216347218865</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.837456370896582</v>
+        <v>3.730570473395092</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.525498203259382</v>
+        <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.690384389501246</v>
+        <v>-5.103020469477134</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.648988023145136</v>
+        <v>1.520293118079201</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.029319787405868</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.143090075702903</v>
+        <v>4.133149707029525</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.848164230292644</v>
+        <v>3.741278332791154</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.712964428167674</v>
+        <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.718691703374517</v>
+        <v>-5.131327783350405</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.82513132250412</v>
+        <v>1.696436417438186</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.029319787405868</v>
+        <v>0.9521532947428711</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.330556300611195</v>
+        <v>4.320615931937818</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.80600151312193</v>
+        <v>3.69911561562044</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.682367379521757</v>
+        <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.885284928488039</v>
+        <v>-5.297921008463927</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.727896983812794</v>
+        <v>1.599202078746859</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8627265622923457</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.200003316897164</v>
+        <v>4.190062948223787</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.815068416787143</v>
+        <v>3.708182519285653</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.686043782183475</v>
+        <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.862249135126473</v>
+        <v>-5.274885215102361</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.740787703819138</v>
+        <v>1.612092798753204</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8627265622923457</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.203679719558882</v>
+        <v>4.193739350885505</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.847467298900964</v>
+        <v>3.740581401399474</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.68366183730697</v>
+        <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.833003154670776</v>
+        <v>-5.245639234646664</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.750104151124912</v>
+        <v>1.621409246058978</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8627265622923457</v>
+        <v>0.7855600696293488</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.201297774682377</v>
+        <v>4.191357406009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.806290539757867</v>
+        <v>3.699404642256377</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.680955076464605</v>
+        <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.939928702548627</v>
+        <v>-5.352564782524516</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.704627171131407</v>
+        <v>1.575932266065472</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7558010144144943</v>
+        <v>0.6786345217514974</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.134435685113302</v>
+        <v>4.124495316439925</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.796828498202498</v>
+        <v>3.689942600701007</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.682383878607839</v>
+        <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.084947261055876</v>
+        <v>-5.497583341031764</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.648048549871741</v>
+        <v>1.519353644805807</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6107824559072458</v>
+        <v>0.5336159632442489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.048853352152187</v>
+        <v>4.038912983478809</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.818738327188509</v>
+        <v>3.711852429687019</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.782315117865592</v>
+        <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.203289026840594</v>
+        <v>-5.615925106816482</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.700643082815607</v>
+        <v>1.571948177749673</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.155196214547674</v>
+        <v>4.145255845874297</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.821764949292302</v>
+        <v>3.714879051790811</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.780100814991531</v>
+        <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.254699449161301</v>
+        <v>-5.66733552913719</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.677864611013263</v>
+        <v>1.549169705947329</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.152981911673613</v>
+        <v>4.143041543000235</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.81164384693883</v>
+        <v>3.70475794943734</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.78000394306582</v>
+        <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.334118900369053</v>
+        <v>-5.746754980344941</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.645999958604452</v>
+        <v>1.517305053538517</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.152885039747902</v>
+        <v>4.142944671074525</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.97377273195735</v>
+        <v>3.736804952298408</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.779997836623863</v>
+        <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.416691361494864</v>
+        <v>-5.842217978262159</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.61296486771217</v>
+        <v>1.479113747929673</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5443020018071389</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.152878933305945</v>
+        <v>4.142938564632567</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.97377273195735</v>
+        <v>3.715372960218011</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.779997836623863</v>
+        <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.416691361494864</v>
+        <v>-5.777842067411444</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.61296486771217</v>
+        <v>1.50296050883257</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.152878933305945</v>
+        <v>4.179660507705607</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.97377273195735</v>
+        <v>3.736089413353547</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.779997836623863</v>
+        <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.416691361494864</v>
+        <v>-5.833211229543638</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.61296486771217</v>
+        <v>1.486546661727419</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.6086779126578541</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.152878933305945</v>
+        <v>4.185394325453334</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.97377273195735</v>
+        <v>3.73682287011329</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.779997836623863</v>
+        <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.416691361494864</v>
+        <v>-5.851429696541246</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.61296486771217</v>
+        <v>1.478797638271308</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.152878933305945</v>
+        <v>4.169868826442761</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.97377273195735</v>
+        <v>3.790272500113699</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.779997836623863</v>
+        <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.416691361494864</v>
+        <v>-5.812746261197316</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.61296486771217</v>
+        <v>1.514145405259199</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.152878933305945</v>
+        <v>4.18974321929308</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.912846965851127</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.779997836623863</v>
+        <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.414000508294682</v>
+        <v>-5.706711265992007</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.614041208992243</v>
+        <v>1.54026010386605</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.152878933305945</v>
+        <v>4.173443919817807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.913065215142359</v>
+        <v>3.794705093307675</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.782428786087909</v>
+        <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.230788845161586</v>
+        <v>-5.523499602858911</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.689756823709527</v>
+        <v>1.615975718583334</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6214684944701359</v>
+        <v>0.5835714754020119</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.155309882769991</v>
+        <v>4.175874869281854</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.89520667969824</v>
+        <v>3.776846557863556</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.765373192167286</v>
+        <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.159067398147736</v>
+        <v>-5.45177815584506</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.701389808594445</v>
+        <v>1.627608703468252</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6931899414839865</v>
+        <v>0.6552929224158626</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.181287157057678</v>
+        <v>4.201852143569541</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.842149827228802</v>
+        <v>3.723789705394118</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.712288938088458</v>
+        <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.136694372540029</v>
+        <v>-5.429405130237354</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.657254764758699</v>
+        <v>1.583473659632506</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7044456925968881</v>
+        <v>0.6665486735287641</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.134956353646591</v>
+        <v>4.155521340158454</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.83396756829142</v>
+        <v>3.715607446456736</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.897487142973813</v>
+        <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.169710668450774</v>
+        <v>-5.462421426148099</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.829246451279756</v>
+        <v>1.755465346153563</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6350083159301365</v>
+        <v>0.5971112968620125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.278492132531896</v>
+        <v>4.299057119043757</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.832122658718371</v>
+        <v>3.713762536883687</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.889408368802063</v>
+        <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.158183032801166</v>
+        <v>-5.45089379049849</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.825778731367849</v>
+        <v>1.751997626241656</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.694008974131499</v>
+        <v>0.6561119550633749</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.305813753280963</v>
+        <v>4.326378739792824</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.939589964586375</v>
+        <v>3.717150699236308</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.893076481323851</v>
+        <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.255731774006746</v>
+        <v>-5.548235291840859</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.790427347407406</v>
+        <v>1.716729138226496</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6489463668615292</v>
+        <v>0.6116917728978866</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.282444301440769</v>
+        <v>4.303394743015319</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.939589964586375</v>
+        <v>3.705201079427695</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.893076481323851</v>
+        <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.255731774006746</v>
+        <v>-5.634091321180826</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.790427347407406</v>
+        <v>1.683637808683348</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6489463668615292</v>
+        <v>0.5693157036717515</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.282444301440769</v>
+        <v>4.279220183672477</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.822819149114461</v>
+        <v>3.691835499610386</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.893076481323851</v>
+        <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.259481139925343</v>
+        <v>-5.642928118596945</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.788927601039966</v>
+        <v>1.662522291537402</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6489463668615292</v>
+        <v>0.5618735310304008</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.282444301440769</v>
+        <v>4.257174081908168</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.84652806117154</v>
+        <v>3.715544411667464</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.903240992368901</v>
+        <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.350863702490802</v>
+        <v>-5.734310681162404</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.762539087058832</v>
+        <v>1.636133777556268</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6123814821421845</v>
+        <v>0.5253086463110561</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.270669881654212</v>
+        <v>4.245399662121611</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.834962531913027</v>
+        <v>3.673978374889202</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.005369250193168</v>
+        <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.352997470856717</v>
+        <v>-5.722603963175398</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.863813837536734</v>
+        <v>1.742944722575339</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.37151787845893</v>
+        <v>4.354551950738083</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.812850798281435</v>
+        <v>3.682476099409577</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.005369250193168</v>
+        <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.351921148956471</v>
+        <v>-5.793516036917675</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.864244366296833</v>
+        <v>1.717612231809833</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.37151787845893</v>
+        <v>4.357584289469488</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.803269876324434</v>
+        <v>3.672895177452576</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.005369250193168</v>
+        <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.351921148956471</v>
+        <v>-5.803832135084027</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.864244366296833</v>
+        <v>1.714304618275557</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.5370153642980625</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.37151787845893</v>
+        <v>4.358403115201752</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.919498914949401</v>
+        <v>3.623960959762297</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.005369250193168</v>
+        <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.351921148956471</v>
+        <v>-5.803738167066654</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.864244366296833</v>
+        <v>1.713520872394595</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.37151787845893</v>
+        <v>4.357803698922233</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.919498914949401</v>
+        <v>3.634813277125781</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.005369250193168</v>
+        <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.351921148956471</v>
+        <v>-5.952104394722799</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.864244366296833</v>
+        <v>1.648406367276491</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.5373852256453805</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.37151787845893</v>
+        <v>4.352035684866586</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.792052432567817</v>
+        <v>3.647901163120264</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.005369250193168</v>
+        <v>4.046625962701006</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.350972725838433</v>
+        <v>-6.078387948780489</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.864623735544048</v>
+        <v>1.614914358875063</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.37151787845893</v>
+        <v>4.293286965653619</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>4.025210556490521</v>
+        <v>3.881059287042968</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.01809685817426</v>
+        <v>4.059353570682098</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.451242543797454</v>
+        <v>-6.17865776673951</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.837243416341531</v>
+        <v>1.587534039672546</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.384245486440022</v>
+        <v>4.306014573634712</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.861216348251665</v>
+        <v>3.717065078804112</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.020042856598648</v>
+        <v>4.061299569106485</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.445250297008642</v>
+        <v>-6.172665519950699</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.841586313481444</v>
+        <v>1.591876936812459</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.38619148486441</v>
+        <v>4.3079605720591</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.886087536976113</v>
+        <v>3.74193626752856</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.013696992616417</v>
+        <v>4.054953705124254</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.356692335877875</v>
+        <v>-6.084107558819931</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.87066363395152</v>
+        <v>1.620954257282535</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.379845620882179</v>
+        <v>4.301614708076869</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.879445911209985</v>
+        <v>3.735294641762432</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.013005670055413</v>
+        <v>4.05426238256325</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.338933258374801</v>
+        <v>-6.066348481316857</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.877075942391745</v>
+        <v>1.62736656572276</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.6102477137762693</v>
+        <v>0.4111016715876899</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.379154298321175</v>
+        <v>4.300923385515864</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.922377337547891</v>
+        <v>3.778226068100338</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.025787855963999</v>
+        <v>4.067044568471837</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.239303107325733</v>
+        <v>-5.966718330267789</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.929710188719959</v>
+        <v>1.680000812050974</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.7098778648253368</v>
+        <v>0.5107318226367574</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.451714574859202</v>
+        <v>4.373483662053892</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.919502287282165</v>
+        <v>3.775351017834612</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.214942121462726</v>
+        <v>4.256198833970563</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.288702616014744</v>
+        <v>-6.0161178389568</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.099104650743081</v>
+        <v>1.849395274074096</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.7201366982570815</v>
+        <v>0.5209906560685021</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.647024140416975</v>
+        <v>4.568793227611665</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.893223248790029</v>
+        <v>3.749071979342476</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.202130794565588</v>
+        <v>4.243387507073425</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.082018142372368</v>
+        <v>-5.809433365314424</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.168967113302894</v>
+        <v>1.919257736633908</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.9268211718994571</v>
+        <v>0.7276751297108778</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.758223497705263</v>
+        <v>4.679992584899952</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.884429578989439</v>
+        <v>3.740278309541886</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.204132308219693</v>
+        <v>4.24538902072753</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.116175037369894</v>
+        <v>-5.843590260311951</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.157305868957988</v>
+        <v>1.907596492289003</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8432374023586446</v>
+        <v>0.6440913601700653</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.71007474963488</v>
+        <v>4.63184383682957</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.926627305479281</v>
+        <v>3.782476036031728</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.55762942220936</v>
+        <v>4.598886134717198</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.023585558308437</v>
+        <v>-5.751000781250494</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.547838774572238</v>
+        <v>2.298129397903253</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8432374023586446</v>
+        <v>0.6440913601700653</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.063571863624547</v>
+        <v>4.985340950819237</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.953201094935572</v>
+        <v>3.809049825488019</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.562192533776464</v>
+        <v>4.603449246284301</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.096746162081582</v>
+        <v>-5.824161385023639</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.523137644630084</v>
+        <v>2.273428267961098</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.6160701601358223</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.051322255171105</v>
+        <v>4.973091342365795</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.908785935266827</v>
+        <v>3.835196361482913</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.612022475099992</v>
+        <v>4.653279187607828</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.050099907305197</v>
+        <v>-5.771945075227297</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.591626087864166</v>
+        <v>2.344144733203162</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.6160701601358223</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.101152196494633</v>
+        <v>5.022921283689322</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.908785935266827</v>
+        <v>3.821821067427094</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.612022475099992</v>
+        <v>4.662093157817839</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.050099907305197</v>
+        <v>-5.719437747716802</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.591626087864166</v>
+        <v>2.373961634417371</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.6685774876463172</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.101152196494633</v>
+        <v>5.06323965040563</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.908785935266827</v>
+        <v>3.825262337030104</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.612022475099992</v>
+        <v>4.657730741857036</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.050099907305197</v>
+        <v>-5.734193071916943</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.591626087864166</v>
+        <v>2.363697088776512</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.6685774876463172</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.101152196494633</v>
+        <v>5.058877234444827</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.908785935266827</v>
+        <v>3.845038586515098</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.612022475099992</v>
+        <v>4.648655245273316</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.050099907305197</v>
+        <v>-5.684728448547031</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.591626087864166</v>
+        <v>2.374407441540756</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.7180421110162288</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.101152196494633</v>
+        <v>5.079480511883053</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.908785935266827</v>
+        <v>3.825925710858572</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.612022475099992</v>
+        <v>4.645062912988251</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.050099907305197</v>
+        <v>-5.521620456393416</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.591626087864166</v>
+        <v>2.436058306117137</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.8811501031698441</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.101152196494633</v>
+        <v>5.173752974890157</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.994720839830584</v>
+        <v>3.847090399223587</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.612022475099992</v>
+        <v>4.654109949679379</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.052850023294524</v>
+        <v>-5.500977365592188</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.590526041468435</v>
+        <v>2.453362579128756</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.8152162023244016</v>
+        <v>0.8811501031698441</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.101152196494633</v>
+        <v>5.182800011581286</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.980050348777287</v>
+        <v>3.832419908170291</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.612879940086113</v>
+        <v>4.6549674146655</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.115557939769082</v>
+        <v>-5.563685282066746</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.566300339864733</v>
+        <v>2.429136877525055</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.7525082858498439</v>
+        <v>0.8184421866952863</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.06438491159602</v>
+        <v>5.146032726682672</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>4.009203760565335</v>
+        <v>3.861573319958338</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.575789356876466</v>
+        <v>4.617876831455852</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.067549815925389</v>
+        <v>-5.515677158223053</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.548413006192563</v>
+        <v>2.411249543852884</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.7525082858498439</v>
+        <v>0.8184421866952863</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.027294328386372</v>
+        <v>5.108942143473024</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>4.019878268616226</v>
+        <v>3.872247828009229</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.579721610434415</v>
+        <v>4.621809085013803</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.917431760703492</v>
+        <v>-5.365559103001156</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.612392481839271</v>
+        <v>2.475229019499593</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9026263410717409</v>
+        <v>0.9685602419171834</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.12129741507746</v>
+        <v>5.202945230164113</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>4.016126892672749</v>
+        <v>3.868496452065752</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.574620703041452</v>
+        <v>4.61670817762084</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.822874249330132</v>
+        <v>-5.271001591627797</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.645114578995652</v>
+        <v>2.507951116655974</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9026263410717409</v>
+        <v>0.9685602419171834</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.116196507684497</v>
+        <v>5.19784432277115</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.914573818819656</v>
+        <v>3.849317964426063</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.569974612430547</v>
+        <v>4.612062087009935</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.714014736096746</v>
+        <v>-5.152828213609869</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.684012293678101</v>
+        <v>2.55057437725224</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.011485854305127</v>
+        <v>1.086733619935111</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.176866125013624</v>
+        <v>5.264102258971001</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.914573818819656</v>
+        <v>3.836457194908351</v>
       </c>
       <c r="C2103" t="n">
-        <v>4.569974612430547</v>
+        <v>4.641150679872962</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.714014736096746</v>
+        <v>-5.063981096750371</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.684012293678101</v>
+        <v>2.615201816859066</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.011485854305127</v>
+        <v>1.175580736794608</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.176866125013624</v>
+        <v>5.346499121949727</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.914573818819656</v>
+        <v>3.805495133363365</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.569974612430547</v>
+        <v>4.634710902884139</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.714014736096746</v>
+        <v>-5.036932059057118</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.684012293678101</v>
+        <v>2.619581654947545</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.011485854305127</v>
+        <v>1.202629774487862</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.176866125013624</v>
+        <v>5.356288767576856</v>
       </c>
     </row>
     <row r="2105">
@@ -49960,22 +49960,22 @@
         <v>45567</v>
       </c>
       <c r="B2105" t="n">
-        <v>3.95400890080217</v>
+        <v>3.800856139580967</v>
       </c>
       <c r="C2105" t="n">
-        <v>4.569974612430547</v>
+        <v>4.60019922025518</v>
       </c>
       <c r="D2105" t="n">
-        <v>-4.720048016283516</v>
+        <v>-5.056249245082641</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.681598981603393</v>
+        <v>2.577343097908377</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.011485854305127</v>
+        <v>1.183312588462339</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.176866125013624</v>
+        <v>5.310186773332584</v>
       </c>
     </row>
     <row r="2106">
@@ -49983,22 +49983,22 @@
         <v>45568</v>
       </c>
       <c r="B2106" t="n">
-        <v>4.040997056470527</v>
+        <v>3.792525897488041</v>
       </c>
       <c r="C2106" t="n">
-        <v>4.57361277957296</v>
+        <v>4.603837387397593</v>
       </c>
       <c r="D2106" t="n">
-        <v>-4.766897045101583</v>
+        <v>-5.108101020655802</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.66649753721858</v>
+        <v>2.560240554821525</v>
       </c>
       <c r="F2106" t="n">
-        <v>0.9646368254870601</v>
+        <v>1.131460812889177</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.152394874865196</v>
+        <v>5.282713875131099</v>
       </c>
     </row>
     <row r="2107">
@@ -50006,22 +50006,22 @@
         <v>45569</v>
       </c>
       <c r="B2107" t="n">
-        <v>3.966927267586609</v>
+        <v>3.807455680748604</v>
       </c>
       <c r="C2107" t="n">
-        <v>4.57361277957296</v>
+        <v>4.56732913458143</v>
       </c>
       <c r="D2107" t="n">
-        <v>-4.76450818731155</v>
+        <v>-5.135158466787629</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.667453080334592</v>
+        <v>2.512909323552631</v>
       </c>
       <c r="F2107" t="n">
-        <v>0.9646368254870601</v>
+        <v>1.131460812889177</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.152394874865196</v>
+        <v>5.246205622314936</v>
       </c>
     </row>
     <row r="2108">
@@ -50029,22 +50029,22 @@
         <v>45570</v>
       </c>
       <c r="B2108" t="n">
-        <v>3.967196738387655</v>
+        <v>3.807725151549651</v>
       </c>
       <c r="C2108" t="n">
-        <v>4.575020729320151</v>
+        <v>4.568737084328621</v>
       </c>
       <c r="D2108" t="n">
-        <v>-4.837789539165425</v>
+        <v>-5.208439818641504</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.639548489340234</v>
+        <v>2.485004732558272</v>
       </c>
       <c r="F2108" t="n">
-        <v>0.9507254033558485</v>
+        <v>1.117549390757966</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.145455971333661</v>
+        <v>5.239266718783401</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.996092160492793</v>
+        <v>3.761768112402391</v>
       </c>
       <c r="C2109" t="n">
-        <v>4.593260942822961</v>
+        <v>4.586977297831431</v>
       </c>
       <c r="D2109" t="n">
-        <v>-4.757146128492393</v>
+        <v>-5.127796407968472</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.690046067112256</v>
+        <v>2.535502310330294</v>
       </c>
       <c r="F2109" t="n">
-        <v>0.9507254033558485</v>
+        <v>1.117549390757966</v>
       </c>
       <c r="G2109" t="n">
-        <v>5.16369618483647</v>
+        <v>5.25750693228621</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241007.xlsx
+++ b/tame_output/ON/bt/strategyON_20241007.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.1%</t>
+          <t>423.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-674.4%</t>
+          <t>-675.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-122.7%</t>
+          <t>-123.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-112.2%</t>
+          <t>-112.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.360186451293727</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.160862811117614</v>
+        <v>-4.166429528281172</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6954849025329342</v>
+        <v>0.6932582156675111</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.360049318729163</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.116489679479045</v>
+        <v>-4.122056396642603</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7130970226237978</v>
+        <v>0.7108703357583748</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.354443112867754</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.081758358160545</v>
+        <v>-4.087325075324102</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7213833452897886</v>
+        <v>0.7191566584243654</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.360824869895558</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.034102627599489</v>
+        <v>-4.039669344763047</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7468273945420156</v>
+        <v>0.7446007076765924</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.365717243270283</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.933584469100734</v>
+        <v>-3.939151186264292</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7919270313162423</v>
+        <v>0.789700344450819</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.352471915746155</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.917679139668381</v>
+        <v>-3.923245856831939</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7850438355650555</v>
+        <v>0.7828171486996323</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.356569618356784</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.872840738059983</v>
+        <v>-3.878407455223541</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8070768988190433</v>
+        <v>0.8048502119536201</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.360730557987862</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.892339194301992</v>
+        <v>-3.897905911465549</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8034384559533181</v>
+        <v>0.8012117690878948</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.366610160515699</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.848136357216091</v>
+        <v>-3.853703074379649</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8269991933155154</v>
+        <v>0.8247725064500921</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.365020160984947</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.855696023053138</v>
+        <v>-3.861262740216696</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8223853274499442</v>
+        <v>0.8201586405845209</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.416267926167986</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.697404605513866</v>
+        <v>-3.702971322677424</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9369496596486926</v>
+        <v>0.9347229727832695</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.414708630762239</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.48976260187939</v>
+        <v>-3.495329319042948</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.018447165696736</v>
+        <v>1.016220478831313</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.409656859000509</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.438730509156862</v>
+        <v>-3.444297226320419</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.033808231024018</v>
+        <v>1.031581544158594</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.426844263093214</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.373506328029656</v>
+        <v>-3.379073045193214</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.077085307567605</v>
+        <v>1.074858620702182</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.422805235392495</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.336079307958522</v>
+        <v>-3.34164602512208</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.088017087895339</v>
+        <v>1.085790401029916</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.424062027723735</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.334721322984977</v>
+        <v>-3.340288040148534</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.089817074215997</v>
+        <v>1.087590387350574</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.584619798744946</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.306308059885093</v>
+        <v>-3.311874777048651</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.261740150477161</v>
+        <v>1.259513463611738</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47367,10 +47367,10 @@
         <v>2.704732707962763</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.23152579886008</v>
+        <v>-3.237092516023638</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.411765964104984</v>
+        <v>1.409539277239561</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.696440683976622</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.205441714596272</v>
+        <v>-3.21100843175983</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.413907573824366</v>
+        <v>1.411680886958943</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47413,10 +47413,10 @@
         <v>2.694633879560401</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.117563801487152</v>
+        <v>-3.12313051865071</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.447251934651793</v>
+        <v>1.44502524778637</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.712188285287193</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.108671340093869</v>
+        <v>-3.114238057257427</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.468363324935898</v>
+        <v>1.466136638070475</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47459,10 +47459,10 @@
         <v>2.704043332691777</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.277147457063747</v>
+        <v>-3.282714174227304</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.392827925552531</v>
+        <v>1.390601238687108</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47482,10 +47482,10 @@
         <v>2.685313029879639</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.830891264434307</v>
+        <v>-2.836457981597865</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.552600099792169</v>
+        <v>1.550373412926745</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.675977052376543</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.808170160751154</v>
+        <v>-2.813736877914712</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.552352563762334</v>
+        <v>1.550125876896911</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.834883178227712</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.937371974045197</v>
+        <v>-2.942938691208755</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.659577964295886</v>
+        <v>1.657351277430463</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
         <v>2.871961000721359</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.963246372519222</v>
+        <v>-2.96881308968278</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.686306027399923</v>
+        <v>1.684079340534499</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.868636356710904</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.956191682304049</v>
+        <v>-2.961758399467607</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.685803259475537</v>
+        <v>1.683576572610114</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.878642510355645</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.929240457977561</v>
+        <v>-2.934807175141119</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.706589902850874</v>
+        <v>1.704363215985451</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.062745642500605</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.950784685808348</v>
+        <v>-2.956351402971906</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.882075343863519</v>
+        <v>1.879848656998096</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.054862337403598</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.97319280361322</v>
+        <v>-2.978759520776778</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.865228791644563</v>
+        <v>1.86300210477914</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.056916336953236</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.00141703919082</v>
+        <v>-3.006983756354378</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.85599309696316</v>
+        <v>1.853766410097737</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.113170054675083</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.01085796507935</v>
+        <v>-3.016424682242908</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.908470444329595</v>
+        <v>1.906243757464172</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.116061149220384</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.217096902867784</v>
+        <v>-3.222663620031342</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.828865963759523</v>
+        <v>1.8266392768941</v>
       </c>
       <c r="F2007" t="n">
         <v>0.9241185524652205</v>
@@ -47735,10 +47735,10 @@
         <v>3.114172962114159</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.29342688046869</v>
+        <v>-3.298993597632248</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.796445785612936</v>
+        <v>1.794219098747513</v>
       </c>
       <c r="F2008" t="n">
         <v>0.9241185524652205</v>
@@ -47758,10 +47758,10 @@
         <v>3.108993191717021</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.448383665868819</v>
+        <v>-3.453950383032377</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.729283301055746</v>
+        <v>1.727056614190323</v>
       </c>
       <c r="F2009" t="n">
         <v>0.7691617670650912</v>
@@ -47781,10 +47781,10 @@
         <v>3.107427201927174</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.609952091396074</v>
+        <v>-3.615518808559632</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.663089941054997</v>
+        <v>1.660863254189574</v>
       </c>
       <c r="F2010" t="n">
         <v>0.6423788432672118</v>
@@ -47804,10 +47804,10 @@
         <v>3.120500608793092</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.718252753266194</v>
+        <v>-3.723819470429751</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.632843083172868</v>
+        <v>1.630616396307444</v>
       </c>
       <c r="F2011" t="n">
         <v>0.6423788432672118</v>
@@ -47827,10 +47827,10 @@
         <v>3.112505805576032</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.877803826029711</v>
+        <v>-3.883370543193268</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.561027850850401</v>
+        <v>1.558801163984977</v>
       </c>
       <c r="F2012" t="n">
         <v>0.4901011764054604</v>
@@ -47850,10 +47850,10 @@
         <v>3.111029846703034</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.905704613139183</v>
+        <v>-3.911271330302741</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.548391577133613</v>
+        <v>1.54616489026819</v>
       </c>
       <c r="F2013" t="n">
         <v>0.4555042522625256</v>
@@ -47873,10 +47873,10 @@
         <v>3.107794290680233</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.028230715842078</v>
+        <v>-4.033797433005635</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.496145580029655</v>
+        <v>1.493918893164232</v>
       </c>
       <c r="F2014" t="n">
         <v>0.3329781495596317</v>
@@ -47896,10 +47896,10 @@
         <v>3.174500250270737</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.258745212027667</v>
+        <v>-4.264311929191224</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.470645741145923</v>
+        <v>1.4684190542805</v>
       </c>
       <c r="F2015" t="n">
         <v>0.102463653374043</v>
@@ -47919,10 +47919,10 @@
         <v>3.314811969272584</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.60749029725211</v>
+        <v>-4.613057014415667</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.471459426057992</v>
+        <v>1.469232739192569</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.006284300544854848</v>
@@ -47942,10 +47942,10 @@
         <v>3.383792238418224</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.761476715028251</v>
+        <v>-4.767043432191808</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.478845128093176</v>
+        <v>1.476618441227753</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.006284300544854848</v>
@@ -47965,10 +47965,10 @@
         <v>3.369843440538344</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.96607614989126</v>
+        <v>-4.971642867054817</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.383056556268093</v>
+        <v>1.380829869402671</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.006284300544854848</v>
@@ -47988,10 +47988,10 @@
         <v>3.381713929593758</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.218551303898984</v>
+        <v>-5.224118021062541</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.293936983720418</v>
+        <v>1.291710296854995</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.006284300544854848</v>
@@ -48011,10 +48011,10 @@
         <v>3.382924464112702</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.511447060378396</v>
+        <v>-5.517013777541953</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.177989215647596</v>
+        <v>1.175762528782174</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.006284300544854848</v>
@@ -48034,10 +48034,10 @@
         <v>3.387046206340024</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.698111188513204</v>
+        <v>-5.703677905676761</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.107445306620995</v>
+        <v>1.105218619755572</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.03302327136941474</v>
@@ -48057,10 +48057,10 @@
         <v>3.382124059076213</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.844131875427166</v>
+        <v>-5.849698592590723</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.044114884591599</v>
+        <v>1.041888197726176</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.04210636316327171</v>
@@ -48080,10 +48080,10 @@
         <v>3.544328115775257</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.935845884536752</v>
+        <v>-5.941412601700309</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.169633337646809</v>
+        <v>1.167406650781386</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.04210636316327171</v>
@@ -48103,10 +48103,10 @@
         <v>3.539174753739071</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.967497543596721</v>
+        <v>-5.973064260760278</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.151819311986635</v>
+        <v>1.149592625121213</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.04727482040771191</v>
@@ -48126,10 +48126,10 @@
         <v>3.549404171307562</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.036563598169658</v>
+        <v>-6.042130315333215</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.134422307725952</v>
+        <v>1.132195620860529</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.1096456979013219</v>
@@ -48149,10 +48149,10 @@
         <v>3.558329809763465</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.138539720418065</v>
+        <v>-6.144106437581622</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.102557497282491</v>
+        <v>1.100330810417069</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.2116218201497295</v>
@@ -48172,10 +48172,10 @@
         <v>3.55048269700764</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.028533436940844</v>
+        <v>-6.034100154104401</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.138712897917555</v>
+        <v>1.136486211052132</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.1884172482324543</v>
@@ -48195,10 +48195,10 @@
         <v>3.554732707729614</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.041063142052723</v>
+        <v>-6.04662985921628</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.137951026594778</v>
+        <v>1.135724339729355</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.2022437476989773</v>
@@ -48218,10 +48218,10 @@
         <v>3.56199359061215</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.739616416580885</v>
+        <v>-5.745183133744442</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.265790599666049</v>
+        <v>1.263563912800626</v>
       </c>
       <c r="F2029" t="n">
         <v>0.09920297777285991</v>
@@ -48241,10 +48241,10 @@
         <v>3.562964768364861</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.764206660816069</v>
+        <v>-5.769773377979626</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.256925679724686</v>
+        <v>1.254698992859264</v>
       </c>
       <c r="F2030" t="n">
         <v>0.09920297777285991</v>
@@ -48264,10 +48264,10 @@
         <v>3.563807672744617</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.713168284809549</v>
+        <v>-5.718735001973106</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.27818393450705</v>
+        <v>1.275957247641627</v>
       </c>
       <c r="F2031" t="n">
         <v>0.09920297777285991</v>
@@ -48287,10 +48287,10 @@
         <v>3.582845771618762</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.684319607986088</v>
+        <v>-5.689886325149645</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.30876150411058</v>
+        <v>1.306534817245157</v>
       </c>
       <c r="F2032" t="n">
         <v>0.1280516545963202</v>
@@ -48310,10 +48310,10 @@
         <v>3.399029767742697</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.587684695967448</v>
+        <v>-5.593251413131005</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.16359946504197</v>
+        <v>1.161372778176547</v>
       </c>
       <c r="F2033" t="n">
         <v>0.2246865666149601</v>
@@ -48333,10 +48333,10 @@
         <v>3.402531811816661</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.518646685018981</v>
+        <v>-5.524213402182538</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.194716713495321</v>
+        <v>1.192490026629899</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2937245775634282</v>
@@ -48356,10 +48356,10 @@
         <v>3.386958630892743</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.499859584650042</v>
+        <v>-5.505426301813599</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.186658372718979</v>
+        <v>1.184431685853557</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3125116779323667</v>
@@ -48379,10 +48379,10 @@
         <v>3.386146341329173</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.422760983108169</v>
+        <v>-5.428327700271726</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.216685523772158</v>
+        <v>1.214458836906735</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3125116779323667</v>
@@ -48402,10 +48402,10 @@
         <v>3.396015120454245</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.433146177998059</v>
+        <v>-5.438712895161616</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.222400224941275</v>
+        <v>1.220173538075852</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3021264830424774</v>
@@ -48425,10 +48425,10 @@
         <v>3.466852126230671</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.451734336720284</v>
+        <v>-5.457301053883841</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.28580196722881</v>
+        <v>1.283575280363387</v>
       </c>
       <c r="F2038" t="n">
         <v>0.283538324320252</v>
@@ -48448,10 +48448,10 @@
         <v>3.463721137048969</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.45203288341632</v>
+        <v>-5.457599600579877</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.282551559368694</v>
+        <v>1.280324872503271</v>
       </c>
       <c r="F2039" t="n">
         <v>0.2832397776242161</v>
@@ -48471,10 +48471,10 @@
         <v>3.468252031988361</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.351209749725892</v>
+        <v>-5.356776466889449</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.327411707784257</v>
+        <v>1.325185020918834</v>
       </c>
       <c r="F2040" t="n">
         <v>0.2957039931085699</v>
@@ -48494,10 +48494,10 @@
         <v>3.468381285466904</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.160428388973484</v>
+        <v>-5.165995106137041</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.403853505563763</v>
+        <v>1.40162681869834</v>
       </c>
       <c r="F2041" t="n">
         <v>0.4864853538609773</v>
@@ -48517,10 +48517,10 @@
         <v>3.4482181312045</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.053465031124063</v>
+        <v>-5.059031748287619</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.426475694441128</v>
+        <v>1.424249007575705</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5449499618207787</v>
@@ -48540,10 +48540,10 @@
         <v>3.483185067816559</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.9981344432223</v>
+        <v>-5.003701160385857</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.483574866213891</v>
+        <v>1.481348179348469</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6002805497225409</v>
@@ -48563,10 +48563,10 @@
         <v>3.476871635717997</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.986080316309337</v>
+        <v>-4.991647033472894</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.482083084880514</v>
+        <v>1.479856398015092</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6123346766355037</v>
@@ -48586,10 +48586,10 @@
         <v>3.478752265902132</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.063435806437306</v>
+        <v>-5.069002523600863</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.453021519013463</v>
+        <v>1.45079483214804</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5349791865075343</v>
@@ -48609,10 +48609,10 @@
         <v>3.491603291780015</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.995387243745776</v>
+        <v>-5.000953960909333</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.493091969967957</v>
+        <v>1.490865283102534</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6030277491990641</v>
@@ -48632,10 +48632,10 @@
         <v>3.511805961953609</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.226987636915277</v>
+        <v>-5.232554354078834</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.420654482873751</v>
+        <v>1.418427796008328</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6030277491990641</v>
@@ -48655,10 +48655,10 @@
         <v>3.495412198020491</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.277039182444497</v>
+        <v>-5.282605899608054</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.384240100728945</v>
+        <v>1.382013413863522</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6030277491990641</v>
@@ -48678,10 +48678,10 @@
         <v>3.455664111613958</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.452146015020942</v>
+        <v>-5.457712732184499</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.274449281291834</v>
+        <v>1.272222594426411</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6030277491990641</v>
@@ -48701,10 +48701,10 @@
         <v>3.462686730610898</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.256045861590419</v>
+        <v>-5.261612578753976</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.359911961660983</v>
+        <v>1.35768527479556</v>
       </c>
       <c r="F2050" t="n">
         <v>0.799127902629587</v>
@@ -48724,10 +48724,10 @@
         <v>3.561857730183802</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.103020469477134</v>
+        <v>-5.108587186640691</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.520293118079201</v>
+        <v>1.518066431213778</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9521532947428711</v>
@@ -48747,10 +48747,10 @@
         <v>3.749323955092095</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.131327783350405</v>
+        <v>-5.136894500513962</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.696436417438186</v>
+        <v>1.694209730572763</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9521532947428711</v>
@@ -48770,10 +48770,10 @@
         <v>3.718726906446177</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.297921008463927</v>
+        <v>-5.303487725627484</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.599202078746859</v>
+        <v>1.596975391881437</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7855600696293488</v>
@@ -48793,10 +48793,10 @@
         <v>3.722403309107895</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.274885215102361</v>
+        <v>-5.280451932265918</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.612092798753204</v>
+        <v>1.609866111887781</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7855600696293488</v>
@@ -48816,10 +48816,10 @@
         <v>3.72002136423139</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.245639234646664</v>
+        <v>-5.251205951810221</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.621409246058978</v>
+        <v>1.619182559193554</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7855600696293488</v>
@@ -48839,10 +48839,10 @@
         <v>3.717314603389025</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.352564782524516</v>
+        <v>-5.358131499688072</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.575932266065472</v>
+        <v>1.573705579200049</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6786345217514974</v>
@@ -48862,10 +48862,10 @@
         <v>3.71874340553226</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.497583341031764</v>
+        <v>-5.503150058195321</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.519353644805807</v>
+        <v>1.517126957940384</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5336159632442489</v>
@@ -48885,10 +48885,10 @@
         <v>3.818674644790013</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.615925106816482</v>
+        <v>-5.621491823980039</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.571948177749673</v>
+        <v>1.56972149088425</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5443020018071389</v>
@@ -48908,10 +48908,10 @@
         <v>3.816460341915952</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.66733552913719</v>
+        <v>-5.672902246300747</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.549169705947329</v>
+        <v>1.546943019081906</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5443020018071389</v>
@@ -48931,10 +48931,10 @@
         <v>3.816363469990241</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.746754980344941</v>
+        <v>-5.752321697508498</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.517305053538517</v>
+        <v>1.515078366673094</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5443020018071389</v>
@@ -48954,10 +48954,10 @@
         <v>3.816357363548284</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.842217978262159</v>
+        <v>-5.847784695425716</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.479113747929673</v>
+        <v>1.47688706106425</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5443020018071389</v>
@@ -48977,10 +48977,10 @@
         <v>3.814453760110895</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.777842067411444</v>
+        <v>-5.783408784575001</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.50296050883257</v>
+        <v>1.500733821967147</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6086779126578541</v>
@@ -49000,10 +49000,10 @@
         <v>3.820187577858621</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.833211229543638</v>
+        <v>-5.838777946707195</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.486546661727419</v>
+        <v>1.484319974861996</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6086779126578541</v>
@@ -49023,10 +49023,10 @@
         <v>3.819725941201554</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.851429696541246</v>
+        <v>-5.856996413704803</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.478797638271308</v>
+        <v>1.476570951405885</v>
       </c>
       <c r="F2064" t="n">
         <v>0.5835714754020119</v>
@@ -49046,10 +49046,10 @@
         <v>3.839600334051872</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.812746261197316</v>
+        <v>-5.818312978360873</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.514145405259199</v>
+        <v>1.511918718393776</v>
       </c>
       <c r="F2065" t="n">
         <v>0.5835714754020119</v>
@@ -49069,10 +49069,10 @@
         <v>3.8233010345766</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.706711265992007</v>
+        <v>-5.712277983155563</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.54026010386605</v>
+        <v>1.538033417000627</v>
       </c>
       <c r="F2066" t="n">
         <v>0.5835714754020119</v>
@@ -49092,10 +49092,10 @@
         <v>3.825731984040646</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.523499602858911</v>
+        <v>-5.529066320022468</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.615975718583334</v>
+        <v>1.613749031717911</v>
       </c>
       <c r="F2067" t="n">
         <v>0.5835714754020119</v>
@@ -49115,10 +49115,10 @@
         <v>3.808676390120023</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.45177815584506</v>
+        <v>-5.457344873008617</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.627608703468252</v>
+        <v>1.625382016602829</v>
       </c>
       <c r="F2068" t="n">
         <v>0.6552929224158626</v>
@@ -49138,10 +49138,10 @@
         <v>3.755592136041195</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.429405130237354</v>
+        <v>-5.434971847400911</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.583473659632506</v>
+        <v>1.581246972767083</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6665486735287641</v>
@@ -49161,10 +49161,10 @@
         <v>3.94079034092655</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.462421426148099</v>
+        <v>-5.467988143311656</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.755465346153563</v>
+        <v>1.75323865928814</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5971112968620125</v>
@@ -49184,10 +49184,10 @@
         <v>3.932711566754799</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.45089379049849</v>
+        <v>-5.456460507662047</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.751997626241656</v>
+        <v>1.749770939376233</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6561119550633749</v>
@@ -49207,10 +49207,10 @@
         <v>3.936379679276587</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.548235291840859</v>
+        <v>-5.553802009004416</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.716729138226496</v>
+        <v>1.714502451361074</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6116917728978866</v>
@@ -49230,10 +49230,10 @@
         <v>3.937630761469426</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.634091321180826</v>
+        <v>-5.639658038344383</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.683637808683348</v>
+        <v>1.681411121817925</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5693157036717515</v>
@@ -49253,10 +49253,10 @@
         <v>3.920049963289927</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.642928118596945</v>
+        <v>-5.648494835760502</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.662522291537402</v>
+        <v>1.660295604671979</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5618735310304008</v>
@@ -49276,10 +49276,10 @@
         <v>3.930214474334977</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.734310681162404</v>
+        <v>-5.739877398325961</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.636133777556268</v>
+        <v>1.633907090690845</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5253086463110561</v>
@@ -49299,10 +49299,10 @@
         <v>4.032342732159245</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.722603963175398</v>
+        <v>-5.728170680338954</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.742944722575339</v>
+        <v>1.740718035709916</v>
       </c>
       <c r="F2076" t="n">
         <v>0.5370153642980625</v>
@@ -49322,10 +49322,10 @@
         <v>4.03537507089065</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.793516036917675</v>
+        <v>-5.799082754081232</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.717612231809833</v>
+        <v>1.71538554494441</v>
       </c>
       <c r="F2077" t="n">
         <v>0.5370153642980625</v>
@@ -49345,10 +49345,10 @@
         <v>4.036193896622915</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.803832135084027</v>
+        <v>-5.809398852247583</v>
       </c>
       <c r="E2078" t="n">
-        <v>1.714304618275557</v>
+        <v>1.712077931410134</v>
       </c>
       <c r="F2078" t="n">
         <v>0.5370153642980625</v>
@@ -49368,10 +49368,10 @@
         <v>4.035372563535004</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.803738167066654</v>
+        <v>-5.809304884230211</v>
       </c>
       <c r="E2079" t="n">
-        <v>1.713520872394595</v>
+        <v>1.711294185529173</v>
       </c>
       <c r="F2079" t="n">
         <v>0.5373852256453805</v>
@@ -49391,10 +49391,10 @@
         <v>4.029604549479358</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.952104394722799</v>
+        <v>-5.957671111886356</v>
       </c>
       <c r="E2080" t="n">
-        <v>1.648406367276491</v>
+        <v>1.646179680411068</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5373852256453805</v>
@@ -49414,10 +49414,10 @@
         <v>4.046625962701006</v>
       </c>
       <c r="D2081" t="n">
-        <v>-6.078387948780489</v>
+        <v>-6.083954665944046</v>
       </c>
       <c r="E2081" t="n">
-        <v>1.614914358875063</v>
+        <v>1.61268767200964</v>
       </c>
       <c r="F2081" t="n">
         <v>0.4111016715876899</v>
@@ -49437,10 +49437,10 @@
         <v>4.059353570682098</v>
       </c>
       <c r="D2082" t="n">
-        <v>-6.17865776673951</v>
+        <v>-6.184224483903067</v>
       </c>
       <c r="E2082" t="n">
-        <v>1.587534039672546</v>
+        <v>1.585307352807123</v>
       </c>
       <c r="F2082" t="n">
         <v>0.4111016715876899</v>
@@ -49460,10 +49460,10 @@
         <v>4.061299569106485</v>
       </c>
       <c r="D2083" t="n">
-        <v>-6.172665519950699</v>
+        <v>-6.178232237114256</v>
       </c>
       <c r="E2083" t="n">
-        <v>1.591876936812459</v>
+        <v>1.589650249947036</v>
       </c>
       <c r="F2083" t="n">
         <v>0.4111016715876899</v>
@@ -49483,10 +49483,10 @@
         <v>4.054953705124254</v>
       </c>
       <c r="D2084" t="n">
-        <v>-6.084107558819931</v>
+        <v>-6.089674275983488</v>
       </c>
       <c r="E2084" t="n">
-        <v>1.620954257282535</v>
+        <v>1.618727570417112</v>
       </c>
       <c r="F2084" t="n">
         <v>0.4111016715876899</v>
@@ -49506,10 +49506,10 @@
         <v>4.05426238256325</v>
       </c>
       <c r="D2085" t="n">
-        <v>-6.066348481316857</v>
+        <v>-6.071915198480414</v>
       </c>
       <c r="E2085" t="n">
-        <v>1.62736656572276</v>
+        <v>1.625139878857337</v>
       </c>
       <c r="F2085" t="n">
         <v>0.4111016715876899</v>
@@ -49529,10 +49529,10 @@
         <v>4.067044568471837</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.966718330267789</v>
+        <v>-5.972285047431346</v>
       </c>
       <c r="E2086" t="n">
-        <v>1.680000812050974</v>
+        <v>1.677774125185551</v>
       </c>
       <c r="F2086" t="n">
         <v>0.5107318226367574</v>
@@ -49552,10 +49552,10 @@
         <v>4.256198833970563</v>
       </c>
       <c r="D2087" t="n">
-        <v>-6.0161178389568</v>
+        <v>-6.021684556120357</v>
       </c>
       <c r="E2087" t="n">
-        <v>1.849395274074096</v>
+        <v>1.847168587208673</v>
       </c>
       <c r="F2087" t="n">
         <v>0.5209906560685021</v>
@@ -49575,10 +49575,10 @@
         <v>4.243387507073425</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.809433365314424</v>
+        <v>-5.815000082477981</v>
       </c>
       <c r="E2088" t="n">
-        <v>1.919257736633908</v>
+        <v>1.917031049768485</v>
       </c>
       <c r="F2088" t="n">
         <v>0.7276751297108778</v>
@@ -49598,10 +49598,10 @@
         <v>4.24538902072753</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.843590260311951</v>
+        <v>-5.849156977475507</v>
       </c>
       <c r="E2089" t="n">
-        <v>1.907596492289003</v>
+        <v>1.90536980542358</v>
       </c>
       <c r="F2089" t="n">
         <v>0.6440913601700653</v>
@@ -49621,10 +49621,10 @@
         <v>4.598886134717198</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.751000781250494</v>
+        <v>-5.756567498414051</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.298129397903253</v>
+        <v>2.29590271103783</v>
       </c>
       <c r="F2090" t="n">
         <v>0.6440913601700653</v>
@@ -49644,10 +49644,10 @@
         <v>4.603449246284301</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.824161385023639</v>
+        <v>-5.829728102187196</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.273428267961098</v>
+        <v>2.271201581095675</v>
       </c>
       <c r="F2091" t="n">
         <v>0.6160701601358223</v>
@@ -49667,10 +49667,10 @@
         <v>4.653279187607828</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.771945075227297</v>
+        <v>-5.777511792390854</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.344144733203162</v>
+        <v>2.34191804633774</v>
       </c>
       <c r="F2092" t="n">
         <v>0.6160701601358223</v>
@@ -49690,10 +49690,10 @@
         <v>4.662093157817839</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.719437747716802</v>
+        <v>-5.725004464880359</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.373961634417371</v>
+        <v>2.371734947551948</v>
       </c>
       <c r="F2093" t="n">
         <v>0.6685774876463172</v>
@@ -49713,10 +49713,10 @@
         <v>4.657730741857036</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.734193071916943</v>
+        <v>-5.7397597890805</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.363697088776512</v>
+        <v>2.361470401911089</v>
       </c>
       <c r="F2094" t="n">
         <v>0.6685774876463172</v>
@@ -49736,10 +49736,10 @@
         <v>4.648655245273316</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.684728448547031</v>
+        <v>-5.690295165710588</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.374407441540756</v>
+        <v>2.372180754675334</v>
       </c>
       <c r="F2095" t="n">
         <v>0.7180421110162288</v>
@@ -49759,10 +49759,10 @@
         <v>4.645062912988251</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.521620456393416</v>
+        <v>-5.527187173556973</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.436058306117137</v>
+        <v>2.433831619251714</v>
       </c>
       <c r="F2096" t="n">
         <v>0.8811501031698441</v>
@@ -49782,10 +49782,10 @@
         <v>4.654109949679379</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.500977365592188</v>
+        <v>-5.506544082755745</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.453362579128756</v>
+        <v>2.451135892263333</v>
       </c>
       <c r="F2097" t="n">
         <v>0.8811501031698441</v>
@@ -49805,10 +49805,10 @@
         <v>4.6549674146655</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.563685282066746</v>
+        <v>-5.569251999230303</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.429136877525055</v>
+        <v>2.426910190659632</v>
       </c>
       <c r="F2098" t="n">
         <v>0.8184421866952863</v>
@@ -49828,10 +49828,10 @@
         <v>4.617876831455852</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.515677158223053</v>
+        <v>-5.52124387538661</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.411249543852884</v>
+        <v>2.409022856987461</v>
       </c>
       <c r="F2099" t="n">
         <v>0.8184421866952863</v>
@@ -49851,10 +49851,10 @@
         <v>4.621809085013803</v>
       </c>
       <c r="D2100" t="n">
-        <v>-5.365559103001156</v>
+        <v>-5.371125820164713</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.475229019499593</v>
+        <v>2.473002332634171</v>
       </c>
       <c r="F2100" t="n">
         <v>0.9685602419171834</v>
@@ -49874,10 +49874,10 @@
         <v>4.61670817762084</v>
       </c>
       <c r="D2101" t="n">
-        <v>-5.271001591627797</v>
+        <v>-5.276568308791354</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.507951116655974</v>
+        <v>2.505724429790551</v>
       </c>
       <c r="F2101" t="n">
         <v>0.9685602419171834</v>
@@ -49897,10 +49897,10 @@
         <v>4.612062087009935</v>
       </c>
       <c r="D2102" t="n">
-        <v>-5.152828213609869</v>
+        <v>-5.158394930773426</v>
       </c>
       <c r="E2102" t="n">
-        <v>2.55057437725224</v>
+        <v>2.548347690386818</v>
       </c>
       <c r="F2102" t="n">
         <v>1.086733619935111</v>
@@ -49920,10 +49920,10 @@
         <v>4.641150679872962</v>
       </c>
       <c r="D2103" t="n">
-        <v>-5.063981096750371</v>
+        <v>-5.069547813913928</v>
       </c>
       <c r="E2103" t="n">
-        <v>2.615201816859066</v>
+        <v>2.612975129993643</v>
       </c>
       <c r="F2103" t="n">
         <v>1.175580736794608</v>
@@ -49943,10 +49943,10 @@
         <v>4.634710902884139</v>
       </c>
       <c r="D2104" t="n">
-        <v>-5.036932059057118</v>
+        <v>-5.042498776220675</v>
       </c>
       <c r="E2104" t="n">
-        <v>2.619581654947545</v>
+        <v>2.617354968082122</v>
       </c>
       <c r="F2104" t="n">
         <v>1.202629774487862</v>
@@ -49966,16 +49966,16 @@
         <v>4.60019922025518</v>
       </c>
       <c r="D2105" t="n">
-        <v>-5.056249245082641</v>
+        <v>-5.068225953794111</v>
       </c>
       <c r="E2105" t="n">
-        <v>2.577343097908377</v>
+        <v>2.572552414423789</v>
       </c>
       <c r="F2105" t="n">
-        <v>1.183312588462339</v>
+        <v>1.176902596914425</v>
       </c>
       <c r="G2105" t="n">
-        <v>5.310186773332584</v>
+        <v>5.306340778403835</v>
       </c>
     </row>
     <row r="2106">
@@ -49989,16 +49989,16 @@
         <v>4.603837387397593</v>
       </c>
       <c r="D2106" t="n">
-        <v>-5.108101020655802</v>
+        <v>-5.120077729367273</v>
       </c>
       <c r="E2106" t="n">
-        <v>2.560240554821525</v>
+        <v>2.555449871336936</v>
       </c>
       <c r="F2106" t="n">
-        <v>1.131460812889177</v>
+        <v>1.125050821341264</v>
       </c>
       <c r="G2106" t="n">
-        <v>5.282713875131099</v>
+        <v>5.278867880202351</v>
       </c>
     </row>
     <row r="2107">
@@ -50012,16 +50012,16 @@
         <v>4.56732913458143</v>
       </c>
       <c r="D2107" t="n">
-        <v>-5.135158466787629</v>
+        <v>-5.147135175499099</v>
       </c>
       <c r="E2107" t="n">
-        <v>2.512909323552631</v>
+        <v>2.508118640068043</v>
       </c>
       <c r="F2107" t="n">
-        <v>1.131460812889177</v>
+        <v>1.125050821341264</v>
       </c>
       <c r="G2107" t="n">
-        <v>5.246205622314936</v>
+        <v>5.242359627386188</v>
       </c>
     </row>
     <row r="2108">
@@ -50035,16 +50035,16 @@
         <v>4.568737084328621</v>
       </c>
       <c r="D2108" t="n">
-        <v>-5.208439818641504</v>
+        <v>-5.220416527352975</v>
       </c>
       <c r="E2108" t="n">
-        <v>2.485004732558272</v>
+        <v>2.480214049073684</v>
       </c>
       <c r="F2108" t="n">
-        <v>1.117549390757966</v>
+        <v>1.111139399210052</v>
       </c>
       <c r="G2108" t="n">
-        <v>5.239266718783401</v>
+        <v>5.235420723854652</v>
       </c>
     </row>
     <row r="2109">
@@ -50052,22 +50052,22 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.761768112402391</v>
+        <v>3.836620573654788</v>
       </c>
       <c r="C2109" t="n">
         <v>4.586977297831431</v>
       </c>
       <c r="D2109" t="n">
-        <v>-5.127796407968472</v>
+        <v>-5.139773116679943</v>
       </c>
       <c r="E2109" t="n">
-        <v>2.535502310330294</v>
+        <v>2.530711626845706</v>
       </c>
       <c r="F2109" t="n">
-        <v>1.117549390757966</v>
+        <v>1.111139399210052</v>
       </c>
       <c r="G2109" t="n">
-        <v>5.25750693228621</v>
+        <v>5.253660937357463</v>
       </c>
     </row>
   </sheetData>
